--- a/frontend/outputs/DataExport_REQ_2026_BC_089_20261011_221106.xlsx
+++ b/frontend/outputs/DataExport_REQ_2026_BC_089_20261011_221106.xlsx
@@ -10,19 +10,26 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DATA_HASIL" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AUDIT_PROVENANCE" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KAMUS_DATA" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PROFILING_KUALITAS_DATA" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DATA_HASIL'!$A$1:$AE$36</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="Rp #,##0"/>
+    <numFmt numFmtId="166" formatCode="#,##0 &quot;transaksi&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="#,##0 &quot;Kolom&quot;"/>
+    <numFmt numFmtId="169" formatCode="#,##0 &quot;Atribut&quot;"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="23">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,6 +45,12 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001E3A8A"/>
       <sz val="10"/>
     </font>
     <font>
@@ -64,8 +77,89 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001E3A8A"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00475569"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00334155"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00334155"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0015803D"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00334155"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="002563EB"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -80,12 +174,40 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
+        <bgColor rgb="00EFF6FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F1F5F9"/>
         <bgColor rgb="00F1F5F9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECFDF5"/>
+        <bgColor rgb="00ECFDF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -107,11 +229,25 @@
         <color rgb="00E2E8F0"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="001E3A8A"/>
+      </top>
+      <bottom style="double">
+        <color rgb="001E3A8A"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -126,17 +262,97 @@
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="16" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="19" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="20" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -502,11 +718,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE36"/>
+  <dimension ref="A1:AE37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="27" customWidth="1" min="5" max="5"/>
@@ -519,18 +735,18 @@
     <col width="30" customWidth="1" min="12" max="12"/>
     <col width="19" customWidth="1" min="13" max="13"/>
     <col width="19" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="41" customWidth="1" min="17" max="17"/>
-    <col width="17" customWidth="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="26" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="20" customWidth="1" min="24" max="24"/>
-    <col width="21" customWidth="1" min="25" max="25"/>
-    <col width="18" customWidth="1" min="26" max="26"/>
+    <col width="26" customWidth="1" min="22" max="22"/>
+    <col width="26" customWidth="1" min="23" max="23"/>
+    <col width="26" customWidth="1" min="24" max="24"/>
+    <col width="26" customWidth="1" min="25" max="25"/>
+    <col width="26" customWidth="1" min="26" max="26"/>
     <col width="14" customWidth="1" min="27" max="27"/>
     <col width="16" customWidth="1" min="28" max="28"/>
     <col width="17" customWidth="1" min="29" max="29"/>
@@ -698,42 +914,42 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>07000000022220260703100001</t>
+          <t>07000000022220260704100001</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>009923</t>
+          <t>001921</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>KPPBC TMP TANJUNG PRIOK</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>KPPBC TMP TANJUNG PERAK</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>KPPBC TMP TANJUNG PERAK</t>
-        </is>
-      </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>PT AST*** AGRO LESTARI</t>
+          <t>PT UNI*** INDONESIA</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>09.201.***.*-772.000</t>
+          <t>01.264.***.*-936.000</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>01.813.***.*-323.000</t>
+          <t>01.813.***.*-707.000</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -748,7 +964,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Tiongkok</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -758,12 +974,12 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Tiongkok</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Tiongkok</t>
         </is>
       </c>
       <c r="O2" s="2" t="n">
@@ -771,16 +987,16 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>7112300000</t>
+          <t>7112999000</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>ANODE SLIME (HASIL PEMURNIAN TEMBAGA)</t>
+          <t>ELECTRONIC SCRAP CONTAINING GOLD</t>
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>5200</v>
+        <v>15400</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -788,7 +1004,7 @@
         </is>
       </c>
       <c r="T2" s="2" t="n">
-        <v>5200</v>
+        <v>15400</v>
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
@@ -799,25 +1015,25 @@
         <v>15500</v>
       </c>
       <c r="W2" s="4" t="n">
-        <v>48000</v>
+        <v>75000</v>
       </c>
       <c r="X2" s="5" t="n">
         <v>0.075</v>
       </c>
       <c r="Y2" s="5" t="n">
-        <v>55800000</v>
+        <v>0</v>
       </c>
       <c r="Z2" s="5" t="n">
-        <v>11160000</v>
+        <v>0</v>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>H</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>MERAH</t>
+          <t>HIJAU</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -832,24 +1048,24 @@
       </c>
       <c r="AE2" s="2" t="inlineStr">
         <is>
-          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-07-03)</t>
+          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-07-04)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>07000000022220260728100002</t>
+          <t>07000000022220260918100002</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>001294</t>
+          <t>003209</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -859,22 +1075,22 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>KPPBC TMP TANJUNG PRIOK</t>
+          <t>KPPBC TMP BELAWAN</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>PT KRA*** STEEL</t>
+          <t>PT IND*** CBP MAKMUR</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>08.191.***.*-402.000</t>
+          <t>08.370.***.*-508.000</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>01.813.***.*-673.000</t>
+          <t>01.813.***.*-575.000</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -889,7 +1105,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Jepang</t>
+          <t>Belanda</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -899,12 +1115,12 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Jepang</t>
+          <t>Belanda</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Jepang</t>
+          <t>Belanda</t>
         </is>
       </c>
       <c r="O3" s="2" t="n">
@@ -912,7 +1128,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>7112999000</t>
+          <t>7112920000</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -921,7 +1137,7 @@
         </is>
       </c>
       <c r="R3" s="2" t="n">
-        <v>5200</v>
+        <v>10650</v>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
@@ -929,7 +1145,7 @@
         </is>
       </c>
       <c r="T3" s="2" t="n">
-        <v>5200</v>
+        <v>10650</v>
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
@@ -940,25 +1156,25 @@
         <v>15500</v>
       </c>
       <c r="W3" s="4" t="n">
-        <v>240000</v>
+        <v>520000</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>0.15</v>
+        <v>0.075</v>
       </c>
       <c r="Y3" s="5" t="n">
-        <v>0</v>
+        <v>604500000</v>
       </c>
       <c r="Z3" s="5" t="n">
-        <v>0</v>
+        <v>120900000</v>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>M</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>HIJAU</t>
+          <t>MERAH</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -973,29 +1189,29 @@
       </c>
       <c r="AE3" s="2" t="inlineStr">
         <is>
-          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-07-28)</t>
+          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-09-18)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07000000022220260703100003</t>
+          <t>07000000022220260908100003</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>005891</t>
+          <t>009233</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>KPPBC TMP SOEKARNO HATTA</t>
+          <t>KPPBC TMP TANJUNG PERAK</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1005,17 +1221,17 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>PT AST*** AGRO LESTARI</t>
+          <t>PT MAY*** INDAH TBK</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>07.940.***.*-637.000</t>
+          <t>07.798.***.*-215.000</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>01.813.***.*-772.000</t>
+          <t>01.813.***.*-475.000</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1030,7 +1246,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Jepang</t>
+          <t>India</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -1040,12 +1256,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Jepang</t>
+          <t>India</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Jepang</t>
+          <t>India</t>
         </is>
       </c>
       <c r="O4" s="2" t="n">
@@ -1053,16 +1269,16 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7112991000</t>
+          <t>7112999000</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>WASTE AND SCRAP OF PRECIOUS METAL</t>
+          <t>SILVER CHAIN SCRAPS</t>
         </is>
       </c>
       <c r="R4" s="2" t="n">
-        <v>5200</v>
+        <v>10650</v>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
@@ -1070,7 +1286,7 @@
         </is>
       </c>
       <c r="T4" s="2" t="n">
-        <v>5200</v>
+        <v>10650</v>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
@@ -1081,16 +1297,16 @@
         <v>15500</v>
       </c>
       <c r="W4" s="4" t="n">
-        <v>75000</v>
+        <v>310000</v>
       </c>
       <c r="X4" s="5" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="Y4" s="5" t="n">
-        <v>58125000</v>
+        <v>480500000</v>
       </c>
       <c r="Z4" s="5" t="n">
-        <v>17437500</v>
+        <v>72075000</v>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
@@ -1114,49 +1330,49 @@
       </c>
       <c r="AE4" s="2" t="inlineStr">
         <is>
-          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-07-03)</t>
+          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-09-08)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07000000022220260908100004</t>
+          <t>07000000022220260927100004</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>007723</t>
+          <t>007506</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>KPPBC TMP BELAWAN</t>
+          <t>KPPBC TMP TANJUNG PRIOK</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>KPPBC TMP BELAWAN</t>
+          <t>KPPBC TMP TANJUNG PERAK</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>PT AST*** AGRO LESTARI</t>
+          <t>PT MAY*** INDAH TBK</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>02.212.***.*-284.000</t>
+          <t>05.789.***.*-382.000</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>01.813.***.*-467.000</t>
+          <t>01.813.***.*-192.000</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1199,11 +1415,11 @@
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>WASTE AND SCRAP OF PRECIOUS METAL</t>
+          <t>ANODE SLIME (HASIL PEMURNIAN TEMBAGA)</t>
         </is>
       </c>
       <c r="R5" s="2" t="n">
-        <v>22000</v>
+        <v>31500</v>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
@@ -1211,7 +1427,7 @@
         </is>
       </c>
       <c r="T5" s="2" t="n">
-        <v>22000</v>
+        <v>31500</v>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
@@ -1222,25 +1438,25 @@
         <v>15500</v>
       </c>
       <c r="W5" s="4" t="n">
-        <v>185000</v>
+        <v>48000</v>
       </c>
       <c r="X5" s="5" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="Y5" s="5" t="n">
-        <v>0</v>
+        <v>37200000</v>
       </c>
       <c r="Z5" s="5" t="n">
-        <v>0</v>
+        <v>11160000</v>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>H</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>KUNING</t>
+          <t>HIJAU</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1255,29 +1471,29 @@
       </c>
       <c r="AE5" s="2" t="inlineStr">
         <is>
-          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-09-08)</t>
+          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-09-27)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>07000000022220260802100005</t>
+          <t>07000000022220260905100005</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>003144</t>
+          <t>006909</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>KPPBC TMP TANJUNG PERAK</t>
+          <t>KPPBC TMP BELAWAN</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1287,17 +1503,17 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>PT AST*** AGRO LESTARI</t>
+          <t>PT IND*** CBP MAKMUR</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>04.348.***.*-297.000</t>
+          <t>03.306.***.*-179.000</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>01.813.***.*-945.000</t>
+          <t>01.813.***.*-868.000</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1312,7 +1528,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>Tiongkok</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1322,12 +1538,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>Tiongkok</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>Tiongkok</t>
         </is>
       </c>
       <c r="O6" s="2" t="n">
@@ -1335,16 +1551,16 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7112300000</t>
+          <t>7112920000</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>WASTE AND SCRAP OF PRECIOUS METAL</t>
+          <t>SILVER CHAIN SCRAPS</t>
         </is>
       </c>
       <c r="R6" s="2" t="n">
-        <v>5200</v>
+        <v>22000</v>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
@@ -1352,7 +1568,7 @@
         </is>
       </c>
       <c r="T6" s="2" t="n">
-        <v>5200</v>
+        <v>22000</v>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
@@ -1363,10 +1579,10 @@
         <v>15500</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>185000</v>
+        <v>48000</v>
       </c>
       <c r="X6" s="5" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="Y6" s="5" t="n">
         <v>0</v>
@@ -1376,12 +1592,12 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>M</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>HIJAU</t>
+          <t>MERAH</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1396,24 +1612,24 @@
       </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-08-02)</t>
+          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-09-05)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>07000000022220260829100006</t>
+          <t>07000000022220260729100006</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>008559</t>
+          <t>004821</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1433,12 +1649,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>08.375.***.*-347.000</t>
+          <t>05.583.***.*-943.000</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>01.813.***.*-968.000</t>
+          <t>01.813.***.*-154.000</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1453,7 +1669,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Jepang</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1463,12 +1679,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Jepang</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Jepang</t>
         </is>
       </c>
       <c r="O7" s="2" t="n">
@@ -1476,16 +1692,16 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7112920000</t>
+          <t>7112991000</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>ELECTRONIC SCRAP CONTAINING GOLD</t>
+          <t>WASTE AND SCRAP OF PRECIOUS METAL</t>
         </is>
       </c>
       <c r="R7" s="2" t="n">
-        <v>10650</v>
+        <v>5200</v>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
@@ -1493,7 +1709,7 @@
         </is>
       </c>
       <c r="T7" s="2" t="n">
-        <v>10650</v>
+        <v>5200</v>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
@@ -1504,25 +1720,25 @@
         <v>15500</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>520000</v>
+        <v>240000</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="Y7" s="5" t="n">
-        <v>403000000</v>
+        <v>0</v>
       </c>
       <c r="Z7" s="5" t="n">
-        <v>120900000</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>H</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>MERAH</t>
+          <t>HIJAU</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1537,49 +1753,49 @@
       </c>
       <c r="AE7" s="2" t="inlineStr">
         <is>
-          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-08-29)</t>
+          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-07-29)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>07000000022220260728100007</t>
+          <t>07000000022220260908100007</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>006133</t>
+          <t>004007</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>KPPBC TMP TANJUNG PERAK</t>
+          <t>KPPBC TMP BELAWAN</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>KPPBC TMP TANJUNG PERAK</t>
+          <t>KPPBC TMP TANJUNG PRIOK</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>PT KAL*** FARMA TBK</t>
+          <t>PT KRA*** STEEL</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>09.437.***.*-173.000</t>
+          <t>04.874.***.*-383.000</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>01.813.***.*-610.000</t>
+          <t>01.813.***.*-616.000</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1594,7 +1810,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Tiongkok</t>
+          <t>Amerika Serikat</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1604,12 +1820,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Tiongkok</t>
+          <t>Amerika Serikat</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Tiongkok</t>
+          <t>Amerika Serikat</t>
         </is>
       </c>
       <c r="O8" s="2" t="n">
@@ -1617,7 +1833,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7112999000</t>
+          <t>7112920000</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1626,7 +1842,7 @@
         </is>
       </c>
       <c r="R8" s="2" t="n">
-        <v>10650</v>
+        <v>22000</v>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
@@ -1634,7 +1850,7 @@
         </is>
       </c>
       <c r="T8" s="2" t="n">
-        <v>10650</v>
+        <v>22000</v>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
@@ -1648,22 +1864,22 @@
         <v>120000</v>
       </c>
       <c r="X8" s="5" t="n">
-        <v>0.075</v>
+        <v>0.1</v>
       </c>
       <c r="Y8" s="5" t="n">
-        <v>139500000</v>
+        <v>186000000</v>
       </c>
       <c r="Z8" s="5" t="n">
         <v>27900000</v>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>H</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>MERAH</t>
+          <t>HIJAU</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1678,49 +1894,49 @@
       </c>
       <c r="AE8" s="2" t="inlineStr">
         <is>
-          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-07-28)</t>
+          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-09-08)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>07000000022220260711100008</t>
+          <t>07000000022220260809100008</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>003450</t>
+          <t>003365</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>KPPBC TMP SOEKARNO HATTA</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>KPPBC TMP BELAWAN</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>KPPBC TMP TANJUNG PERAK</t>
-        </is>
-      </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>PT MAY*** INDAH TBK</t>
+          <t>PT KRA*** STEEL</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>03.717.***.*-169.000</t>
+          <t>08.317.***.*-302.000</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>01.813.***.*-710.000</t>
+          <t>01.813.***.*-262.000</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1735,7 +1951,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>India</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1745,12 +1961,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>India</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>India</t>
         </is>
       </c>
       <c r="O9" s="2" t="n">
@@ -1758,16 +1974,16 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7112999000</t>
+          <t>7112991000</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>WASTE AND SCRAP OF PRECIOUS METAL</t>
+          <t>SILVER CHAIN SCRAPS</t>
         </is>
       </c>
       <c r="R9" s="2" t="n">
-        <v>5200</v>
+        <v>10650</v>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
@@ -1775,7 +1991,7 @@
         </is>
       </c>
       <c r="T9" s="2" t="n">
-        <v>5200</v>
+        <v>10650</v>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
@@ -1786,25 +2002,25 @@
         <v>15500</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>240000</v>
+        <v>185000</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>0.075</v>
+        <v>0.1</v>
       </c>
       <c r="Y9" s="5" t="n">
-        <v>279000000</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="5" t="n">
-        <v>55800000</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>H</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>KUNING</t>
+          <t>HIJAU</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1819,49 +2035,49 @@
       </c>
       <c r="AE9" s="2" t="inlineStr">
         <is>
-          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-07-11)</t>
+          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-08-09)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>07000000022220260703100009</t>
+          <t>07000000022220260825100009</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>006136</t>
+          <t>008553</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>KPPBC TMP SOEKARNO HATTA</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>KPPBC TMP BELAWAN</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>KPPBC TMP TANJUNG PERAK</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>PT AST*** AGRO LESTARI</t>
+          <t>PT IND*** CBP MAKMUR</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>01.449.***.*-673.000</t>
+          <t>09.652.***.*-770.000</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>01.813.***.*-476.000</t>
+          <t>01.813.***.*-909.000</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1876,7 +2092,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Belanda</t>
+          <t>India</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1886,12 +2102,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Belanda</t>
+          <t>India</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Belanda</t>
+          <t>India</t>
         </is>
       </c>
       <c r="O10" s="2" t="n">
@@ -1899,16 +2115,16 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7112991000</t>
+          <t>7112999000</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>ANODE SLIME (HASIL PEMURNIAN TEMBAGA)</t>
+          <t>SILVER CHAIN SCRAPS</t>
         </is>
       </c>
       <c r="R10" s="2" t="n">
-        <v>10650</v>
+        <v>5200</v>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
@@ -1916,7 +2132,7 @@
         </is>
       </c>
       <c r="T10" s="2" t="n">
-        <v>10650</v>
+        <v>5200</v>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
@@ -1927,25 +2143,25 @@
         <v>15500</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>520000</v>
+        <v>120000</v>
       </c>
       <c r="X10" s="5" t="n">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="Y10" s="5" t="n">
-        <v>1209000000</v>
+        <v>93000000</v>
       </c>
       <c r="Z10" s="5" t="n">
-        <v>120900000</v>
+        <v>27900000</v>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>K</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>HIJAU</t>
+          <t>KUNING</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1960,24 +2176,24 @@
       </c>
       <c r="AE10" s="2" t="inlineStr">
         <is>
-          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-07-03)</t>
+          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-08-25)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>07000000022220260808100010</t>
+          <t>07000000022220260918100010</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>008332</t>
+          <t>004766</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1987,22 +2203,22 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>KPPBC TMP TANJUNG PRIOK</t>
+          <t>KPPBC TMP BELAWAN</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>PT KRA*** STEEL</t>
+          <t>PT MAY*** INDAH TBK</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>07.906.***.*-836.000</t>
+          <t>04.573.***.*-857.000</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>01.813.***.*-253.000</t>
+          <t>01.813.***.*-500.000</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2017,7 +2233,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>India</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -2027,12 +2243,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>India</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>India</t>
         </is>
       </c>
       <c r="O11" s="2" t="n">
@@ -2040,16 +2256,16 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7112999000</t>
+          <t>7112991000</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>SILVER CHAIN SCRAPS</t>
+          <t>ANODE SLIME (HASIL PEMURNIAN TEMBAGA)</t>
         </is>
       </c>
       <c r="R11" s="2" t="n">
-        <v>15400</v>
+        <v>22000</v>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
@@ -2057,7 +2273,7 @@
         </is>
       </c>
       <c r="T11" s="2" t="n">
-        <v>15400</v>
+        <v>22000</v>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
@@ -2068,16 +2284,16 @@
         <v>15500</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>48000</v>
+        <v>120000</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="Y11" s="5" t="n">
-        <v>111600000</v>
+        <v>93000000</v>
       </c>
       <c r="Z11" s="5" t="n">
-        <v>11160000</v>
+        <v>27900000</v>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
@@ -2101,29 +2317,29 @@
       </c>
       <c r="AE11" s="2" t="inlineStr">
         <is>
-          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-08-08)</t>
+          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-09-18)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>07000000022220260725100011</t>
+          <t>07000000022220260726100011</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>006833</t>
+          <t>005207</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>KPPBC TMP TANJUNG PERAK</t>
+          <t>KPPBC TMP TANJUNG PRIOK</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2133,17 +2349,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>PT IND*** CBP MAKMUR</t>
+          <t>PT AST*** AGRO LESTARI</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>04.958.***.*-508.000</t>
+          <t>03.394.***.*-592.000</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>01.813.***.*-153.000</t>
+          <t>01.813.***.*-615.000</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2158,7 +2374,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Jepang</t>
+          <t>Singapura</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -2168,12 +2384,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Jepang</t>
+          <t>Singapura</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Jepang</t>
+          <t>Singapura</t>
         </is>
       </c>
       <c r="O12" s="2" t="n">
@@ -2181,16 +2397,16 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7112300000</t>
+          <t>7112991000</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>ANODE SLIME (HASIL PEMURNIAN TEMBAGA)</t>
+          <t>WASTE AND SCRAP OF PRECIOUS METAL</t>
         </is>
       </c>
       <c r="R12" s="2" t="n">
-        <v>15400</v>
+        <v>10650</v>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
@@ -2198,7 +2414,7 @@
         </is>
       </c>
       <c r="T12" s="2" t="n">
-        <v>15400</v>
+        <v>10650</v>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
@@ -2209,16 +2425,16 @@
         <v>15500</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>48000</v>
+        <v>520000</v>
       </c>
       <c r="X12" s="5" t="n">
         <v>0.1</v>
       </c>
       <c r="Y12" s="5" t="n">
-        <v>0</v>
+        <v>806000000</v>
       </c>
       <c r="Z12" s="5" t="n">
-        <v>0</v>
+        <v>120900000</v>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
@@ -2242,24 +2458,24 @@
       </c>
       <c r="AE12" s="2" t="inlineStr">
         <is>
-          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-07-25)</t>
+          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-07-26)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>07000000022220260905100012</t>
+          <t>07000000022220260731100012</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>003211</t>
+          <t>008407</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -2269,22 +2485,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>KPPBC TMP TANJUNG PRIOK</t>
+          <t>KPPBC TMP BELAWAN</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>PT MAY*** INDAH TBK</t>
+          <t>PT KAL*** FARMA TBK</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>05.253.***.*-642.000</t>
+          <t>06.368.***.*-236.000</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>01.813.***.*-678.000</t>
+          <t>01.813.***.*-162.000</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2322,16 +2538,16 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7112991000</t>
+          <t>7112300000</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>ANODE SLIME (HASIL PEMURNIAN TEMBAGA)</t>
+          <t>SILVER CHAIN SCRAPS</t>
         </is>
       </c>
       <c r="R13" s="2" t="n">
-        <v>22000</v>
+        <v>15400</v>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
@@ -2339,7 +2555,7 @@
         </is>
       </c>
       <c r="T13" s="2" t="n">
-        <v>22000</v>
+        <v>15400</v>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
@@ -2353,7 +2569,7 @@
         <v>120000</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="Y13" s="5" t="n">
         <v>0</v>
@@ -2363,12 +2579,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>H</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>KUNING</t>
+          <t>HIJAU</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2383,29 +2599,29 @@
       </c>
       <c r="AE13" s="2" t="inlineStr">
         <is>
-          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-09-05)</t>
+          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-07-31)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>07000000022220260923100013</t>
+          <t>07000000022220260725100013</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>006765</t>
+          <t>005579</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>KPPBC TMP TANJUNG PERAK</t>
+          <t>KPPBC TMP TANJUNG PRIOK</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -2415,17 +2631,17 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>PT KAL*** FARMA TBK</t>
+          <t>PT IND*** CBP MAKMUR</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>09.143.***.*-668.000</t>
+          <t>05.662.***.*-567.000</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>01.813.***.*-756.000</t>
+          <t>01.813.***.*-990.000</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2440,7 +2656,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Amerika Serikat</t>
+          <t>Tiongkok</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -2450,12 +2666,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Amerika Serikat</t>
+          <t>Tiongkok</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Amerika Serikat</t>
+          <t>Tiongkok</t>
         </is>
       </c>
       <c r="O14" s="2" t="n">
@@ -2463,16 +2679,16 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7112991000</t>
+          <t>7112999000</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>ELECTRONIC SCRAP CONTAINING GOLD</t>
+          <t>SILVER CHAIN SCRAPS</t>
         </is>
       </c>
       <c r="R14" s="2" t="n">
-        <v>22000</v>
+        <v>10650</v>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
@@ -2480,7 +2696,7 @@
         </is>
       </c>
       <c r="T14" s="2" t="n">
-        <v>22000</v>
+        <v>10650</v>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
@@ -2491,16 +2707,16 @@
         <v>15500</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>48000</v>
+        <v>520000</v>
       </c>
       <c r="X14" s="5" t="n">
         <v>0.05</v>
       </c>
       <c r="Y14" s="5" t="n">
-        <v>37200000</v>
+        <v>403000000</v>
       </c>
       <c r="Z14" s="5" t="n">
-        <v>11160000</v>
+        <v>120900000</v>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
@@ -2524,24 +2740,24 @@
       </c>
       <c r="AE14" s="2" t="inlineStr">
         <is>
-          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-09-23)</t>
+          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-07-25)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>07000000022220260903100014</t>
+          <t>07000000022220260830100014</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>001290</t>
+          <t>003928</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2561,12 +2777,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>08.584.***.*-620.000</t>
+          <t>06.347.***.*-450.000</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>01.813.***.*-244.000</t>
+          <t>01.813.***.*-260.000</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2581,7 +2797,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Singapura</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -2591,12 +2807,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Singapura</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Singapura</t>
         </is>
       </c>
       <c r="O15" s="2" t="n">
@@ -2604,16 +2820,16 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>7112991000</t>
+          <t>7112999000</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>ANODE SLIME (HASIL PEMURNIAN TEMBAGA)</t>
+          <t>SILVER CHAIN SCRAPS</t>
         </is>
       </c>
       <c r="R15" s="2" t="n">
-        <v>31500</v>
+        <v>10650</v>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
@@ -2621,7 +2837,7 @@
         </is>
       </c>
       <c r="T15" s="2" t="n">
-        <v>31500</v>
+        <v>10650</v>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
@@ -2635,13 +2851,13 @@
         <v>25000</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>0.15</v>
+        <v>0.075</v>
       </c>
       <c r="Y15" s="5" t="n">
-        <v>0</v>
+        <v>29062500</v>
       </c>
       <c r="Z15" s="5" t="n">
-        <v>0</v>
+        <v>5812500</v>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
@@ -2665,49 +2881,49 @@
       </c>
       <c r="AE15" s="2" t="inlineStr">
         <is>
-          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-09-03)</t>
+          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-08-30)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>07000000022220260708100015</t>
+          <t>07000000022220260923100015</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>006735</t>
+          <t>002714</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>KPPBC TMP BELAWAN</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>KPPBC TMP TANJUNG PRIOK</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>KPPBC TMP TANJUNG PERAK</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>PT UNI*** INDONESIA</t>
+          <t>PT MAY*** INDAH TBK</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>07.685.***.*-838.000</t>
+          <t>06.272.***.*-835.000</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>01.813.***.*-456.000</t>
+          <t>01.813.***.*-188.000</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2722,7 +2938,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2732,12 +2948,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="O16" s="2" t="n">
@@ -2745,7 +2961,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7112920000</t>
+          <t>7112300000</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2754,7 +2970,7 @@
         </is>
       </c>
       <c r="R16" s="2" t="n">
-        <v>22000</v>
+        <v>5200</v>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
@@ -2762,7 +2978,7 @@
         </is>
       </c>
       <c r="T16" s="2" t="n">
-        <v>22000</v>
+        <v>5200</v>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
@@ -2773,25 +2989,25 @@
         <v>15500</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>75000</v>
+        <v>120000</v>
       </c>
       <c r="X16" s="5" t="n">
         <v>0.15</v>
       </c>
       <c r="Y16" s="5" t="n">
-        <v>0</v>
+        <v>279000000</v>
       </c>
       <c r="Z16" s="5" t="n">
-        <v>0</v>
+        <v>27900000</v>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>K</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>HIJAU</t>
+          <t>KUNING</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2806,29 +3022,29 @@
       </c>
       <c r="AE16" s="2" t="inlineStr">
         <is>
-          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-07-08)</t>
+          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-09-23)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>07000000022220260811100016</t>
+          <t>07000000022220260727100016</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>005184</t>
+          <t>009646</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>KPPBC TMP SOEKARNO HATTA</t>
+          <t>KPPBC TMP TANJUNG PRIOK</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2838,17 +3054,17 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>PT MAY*** INDAH TBK</t>
+          <t>PT KAL*** FARMA TBK</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>01.694.***.*-533.000</t>
+          <t>09.569.***.*-990.000</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>01.813.***.*-349.000</t>
+          <t>01.813.***.*-135.000</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2863,7 +3079,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Belanda</t>
+          <t>India</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2873,12 +3089,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Belanda</t>
+          <t>India</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Belanda</t>
+          <t>India</t>
         </is>
       </c>
       <c r="O17" s="2" t="n">
@@ -2891,11 +3107,11 @@
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>SILVER CHAIN SCRAPS</t>
+          <t>ELECTRONIC SCRAP CONTAINING GOLD</t>
         </is>
       </c>
       <c r="R17" s="2" t="n">
-        <v>10650</v>
+        <v>5200</v>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
@@ -2903,7 +3119,7 @@
         </is>
       </c>
       <c r="T17" s="2" t="n">
-        <v>10650</v>
+        <v>5200</v>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
@@ -2914,16 +3130,16 @@
         <v>15500</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>48000</v>
+        <v>185000</v>
       </c>
       <c r="X17" s="5" t="n">
         <v>0.1</v>
       </c>
       <c r="Y17" s="5" t="n">
-        <v>74400000</v>
+        <v>0</v>
       </c>
       <c r="Z17" s="5" t="n">
-        <v>11160000</v>
+        <v>0</v>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
@@ -2947,49 +3163,49 @@
       </c>
       <c r="AE17" s="2" t="inlineStr">
         <is>
-          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-08-11)</t>
+          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-07-27)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>07000000022220260710100017</t>
+          <t>07000000022220260731100017</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>005083</t>
+          <t>005471</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>KPPBC TMP TANJUNG PERAK</t>
+          <t>KPPBC TMP BELAWAN</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>KPPBC TMP BELAWAN</t>
+          <t>KPPBC TMP TANJUNG PRIOK</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>PT KRA*** STEEL</t>
+          <t>PT IND*** CBP MAKMUR</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>03.300.***.*-223.000</t>
+          <t>06.816.***.*-634.000</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>01.813.***.*-636.000</t>
+          <t>01.813.***.*-156.000</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -3004,7 +3220,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Amerika Serikat</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -3014,12 +3230,12 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Amerika Serikat</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Amerika Serikat</t>
         </is>
       </c>
       <c r="O18" s="2" t="n">
@@ -3027,16 +3243,16 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7112920000</t>
+          <t>7112300000</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>WASTE AND SCRAP OF PRECIOUS METAL</t>
+          <t>SILVER CHAIN SCRAPS</t>
         </is>
       </c>
       <c r="R18" s="2" t="n">
-        <v>15400</v>
+        <v>5200</v>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
@@ -3044,7 +3260,7 @@
         </is>
       </c>
       <c r="T18" s="2" t="n">
-        <v>15400</v>
+        <v>5200</v>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
@@ -3055,25 +3271,25 @@
         <v>15500</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>185000</v>
+        <v>520000</v>
       </c>
       <c r="X18" s="5" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="Y18" s="5" t="n">
-        <v>286750000</v>
+        <v>0</v>
       </c>
       <c r="Z18" s="5" t="n">
-        <v>43012500</v>
+        <v>0</v>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>M</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>KUNING</t>
+          <t>MERAH</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -3088,24 +3304,24 @@
       </c>
       <c r="AE18" s="2" t="inlineStr">
         <is>
-          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-07-10)</t>
+          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-07-31)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>07000000022220260915100018</t>
+          <t>07000000022220260909100018</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>005870</t>
+          <t>002883</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -3115,22 +3331,22 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>KPPBC TMP TANJUNG PERAK</t>
+          <t>KPPBC TMP BELAWAN</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>PT UNI*** INDONESIA</t>
+          <t>PT AST*** AGRO LESTARI</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>05.252.***.*-555.000</t>
+          <t>05.549.***.*-568.000</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>01.813.***.*-918.000</t>
+          <t>01.813.***.*-504.000</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -3145,7 +3361,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapura</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -3155,12 +3371,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapura</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapura</t>
         </is>
       </c>
       <c r="O19" s="2" t="n">
@@ -3168,16 +3384,16 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7112991000</t>
+          <t>7112300000</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>SILVER CHAIN SCRAPS</t>
+          <t>WASTE AND SCRAP OF PRECIOUS METAL</t>
         </is>
       </c>
       <c r="R19" s="2" t="n">
-        <v>22000</v>
+        <v>5200</v>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
@@ -3185,7 +3401,7 @@
         </is>
       </c>
       <c r="T19" s="2" t="n">
-        <v>22000</v>
+        <v>5200</v>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
@@ -3199,10 +3415,10 @@
         <v>185000</v>
       </c>
       <c r="X19" s="5" t="n">
-        <v>0.05</v>
+        <v>0.075</v>
       </c>
       <c r="Y19" s="5" t="n">
-        <v>143375000</v>
+        <v>215062500</v>
       </c>
       <c r="Z19" s="5" t="n">
         <v>43012500</v>
@@ -3229,49 +3445,49 @@
       </c>
       <c r="AE19" s="2" t="inlineStr">
         <is>
-          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-09-15)</t>
+          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-09-09)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>07000000022220260805100019</t>
+          <t>07000000022220260808100019</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>005580</t>
+          <t>001025</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>KPPBC TMP BELAWAN</t>
+          <t>KPPBC TMP TANJUNG PERAK</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>KPPBC TMP BELAWAN</t>
+          <t>KPPBC TMP TANJUNG PRIOK</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>PT MAY*** INDAH TBK</t>
+          <t>PT KAL*** FARMA TBK</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>04.371.***.*-740.000</t>
+          <t>06.929.***.*-943.000</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>01.813.***.*-409.000</t>
+          <t>01.813.***.*-561.000</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -3286,7 +3502,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>Amerika Serikat</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -3296,12 +3512,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>Amerika Serikat</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>Amerika Serikat</t>
         </is>
       </c>
       <c r="O20" s="2" t="n">
@@ -3309,16 +3525,16 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7112999000</t>
+          <t>7112920000</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>SILVER CHAIN SCRAPS</t>
+          <t>ELECTRONIC SCRAP CONTAINING GOLD</t>
         </is>
       </c>
       <c r="R20" s="2" t="n">
-        <v>5200</v>
+        <v>10650</v>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
@@ -3326,7 +3542,7 @@
         </is>
       </c>
       <c r="T20" s="2" t="n">
-        <v>5200</v>
+        <v>10650</v>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
@@ -3337,16 +3553,16 @@
         <v>15500</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>48000</v>
+        <v>185000</v>
       </c>
       <c r="X20" s="5" t="n">
-        <v>0.075</v>
+        <v>0.15</v>
       </c>
       <c r="Y20" s="5" t="n">
-        <v>55800000</v>
+        <v>430125000</v>
       </c>
       <c r="Z20" s="5" t="n">
-        <v>11160000</v>
+        <v>43012500</v>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
@@ -3370,29 +3586,29 @@
       </c>
       <c r="AE20" s="2" t="inlineStr">
         <is>
-          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-08-05)</t>
+          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-08-08)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>07000000022220260816100020</t>
+          <t>07000000022220260922100020</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>007082</t>
+          <t>003461</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>KPPBC TMP BELAWAN</t>
+          <t>KPPBC TMP TANJUNG PRIOK</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -3407,12 +3623,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>03.649.***.*-723.000</t>
+          <t>05.318.***.*-555.000</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>01.813.***.*-841.000</t>
+          <t>01.813.***.*-870.000</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -3427,7 +3643,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Tiongkok</t>
+          <t>India</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -3437,12 +3653,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Tiongkok</t>
+          <t>India</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Tiongkok</t>
+          <t>India</t>
         </is>
       </c>
       <c r="O21" s="2" t="n">
@@ -3455,11 +3671,11 @@
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>SILVER CHAIN SCRAPS</t>
+          <t>ELECTRONIC SCRAP CONTAINING GOLD</t>
         </is>
       </c>
       <c r="R21" s="2" t="n">
-        <v>15400</v>
+        <v>31500</v>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
@@ -3467,7 +3683,7 @@
         </is>
       </c>
       <c r="T21" s="2" t="n">
-        <v>15400</v>
+        <v>31500</v>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
@@ -3481,22 +3697,22 @@
         <v>75000</v>
       </c>
       <c r="X21" s="5" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="Y21" s="5" t="n">
-        <v>174375000</v>
+        <v>0</v>
       </c>
       <c r="Z21" s="5" t="n">
-        <v>17437500</v>
+        <v>0</v>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>H</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>KUNING</t>
+          <t>HIJAU</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3511,34 +3727,34 @@
       </c>
       <c r="AE21" s="2" t="inlineStr">
         <is>
-          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-08-16)</t>
+          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-09-22)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>07000000022220260929100021</t>
+          <t>07000000022220260803100021</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>006353</t>
+          <t>006951</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>KPPBC TMP TANJUNG PRIOK</t>
+          <t>KPPBC TMP TANJUNG PERAK</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>KPPBC TMP TANJUNG PRIOK</t>
+          <t>KPPBC TMP BELAWAN</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -3548,12 +3764,12 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>03.441.***.*-915.000</t>
+          <t>07.837.***.*-622.000</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>01.813.***.*-580.000</t>
+          <t>01.813.***.*-274.000</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -3568,7 +3784,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Belanda</t>
+          <t>Jepang</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -3578,12 +3794,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>Belanda</t>
+          <t>Jepang</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Belanda</t>
+          <t>Jepang</t>
         </is>
       </c>
       <c r="O22" s="2" t="n">
@@ -3591,16 +3807,16 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7112300000</t>
+          <t>7112999000</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>SILVER CHAIN SCRAPS</t>
+          <t>ANODE SLIME (HASIL PEMURNIAN TEMBAGA)</t>
         </is>
       </c>
       <c r="R22" s="2" t="n">
-        <v>31500</v>
+        <v>10650</v>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
@@ -3608,7 +3824,7 @@
         </is>
       </c>
       <c r="T22" s="2" t="n">
-        <v>31500</v>
+        <v>10650</v>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
@@ -3619,16 +3835,16 @@
         <v>15500</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>75000</v>
+        <v>25000</v>
       </c>
       <c r="X22" s="5" t="n">
-        <v>0.1</v>
+        <v>0.075</v>
       </c>
       <c r="Y22" s="5" t="n">
-        <v>116250000</v>
+        <v>0</v>
       </c>
       <c r="Z22" s="5" t="n">
-        <v>17437500</v>
+        <v>0</v>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
@@ -3652,34 +3868,34 @@
       </c>
       <c r="AE22" s="2" t="inlineStr">
         <is>
-          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-09-29)</t>
+          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-08-03)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>07000000022220260714100022</t>
+          <t>07000000022220260923100022</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>003263</t>
+          <t>008559</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>KPPBC TMP BELAWAN</t>
+          <t>KPPBC TMP TANJUNG PRIOK</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>KPPBC TMP TANJUNG PERAK</t>
+          <t>KPPBC TMP TANJUNG PRIOK</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -3689,12 +3905,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>01.476.***.*-634.000</t>
+          <t>05.848.***.*-988.000</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>01.813.***.*-988.000</t>
+          <t>01.813.***.*-125.000</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -3709,7 +3925,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Jepang</t>
+          <t>Singapura</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -3719,12 +3935,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>Jepang</t>
+          <t>Singapura</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Jepang</t>
+          <t>Singapura</t>
         </is>
       </c>
       <c r="O23" s="2" t="n">
@@ -3737,7 +3953,7 @@
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>ELECTRONIC SCRAP CONTAINING GOLD</t>
+          <t>ANODE SLIME (HASIL PEMURNIAN TEMBAGA)</t>
         </is>
       </c>
       <c r="R23" s="2" t="n">
@@ -3760,10 +3976,10 @@
         <v>15500</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>520000</v>
+        <v>240000</v>
       </c>
       <c r="X23" s="5" t="n">
-        <v>0.1</v>
+        <v>0.075</v>
       </c>
       <c r="Y23" s="5" t="n">
         <v>0</v>
@@ -3773,12 +3989,12 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>H</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>MERAH</t>
+          <t>HIJAU</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3793,36 +4009,36 @@
       </c>
       <c r="AE23" s="2" t="inlineStr">
         <is>
-          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-07-14)</t>
+          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-09-23)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>07000000022220260709100023</t>
+          <t>07000000022220260930100023</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>004888</t>
+          <t>006379</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>KPPBC TMP TANJUNG PRIOK</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>KPPBC TMP TANJUNG PERAK</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>KPPBC TMP TANJUNG PERAK</t>
-        </is>
-      </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
           <t>PT KAL*** FARMA TBK</t>
@@ -3830,12 +4046,12 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>01.195.***.*-991.000</t>
+          <t>04.709.***.*-610.000</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>01.813.***.*-909.000</t>
+          <t>01.813.***.*-556.000</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3850,7 +4066,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Tiongkok</t>
+          <t>Jepang</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3860,12 +4076,12 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>Tiongkok</t>
+          <t>Jepang</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Tiongkok</t>
+          <t>Jepang</t>
         </is>
       </c>
       <c r="O24" s="2" t="n">
@@ -3878,7 +4094,7 @@
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>WASTE AND SCRAP OF PRECIOUS METAL</t>
+          <t>ANODE SLIME (HASIL PEMURNIAN TEMBAGA)</t>
         </is>
       </c>
       <c r="R24" s="2" t="n">
@@ -3901,25 +4117,25 @@
         <v>15500</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>185000</v>
+        <v>25000</v>
       </c>
       <c r="X24" s="5" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="Y24" s="5" t="n">
-        <v>0</v>
+        <v>19375000</v>
       </c>
       <c r="Z24" s="5" t="n">
-        <v>0</v>
+        <v>5812500</v>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>K</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>HIJAU</t>
+          <t>KUNING</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3934,29 +4150,29 @@
       </c>
       <c r="AE24" s="2" t="inlineStr">
         <is>
-          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-07-09)</t>
+          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-09-30)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>07000000022220260911100024</t>
+          <t>07000000022220260901100024</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>002862</t>
+          <t>005231</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>KPPBC TMP BELAWAN</t>
+          <t>KPPBC TMP TANJUNG PRIOK</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3966,17 +4182,17 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>PT UNI*** INDONESIA</t>
+          <t>PT AST*** AGRO LESTARI</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>06.876.***.*-605.000</t>
+          <t>05.495.***.*-982.000</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>01.813.***.*-130.000</t>
+          <t>01.813.***.*-657.000</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3991,7 +4207,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Tiongkok</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -4001,12 +4217,12 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Tiongkok</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Tiongkok</t>
         </is>
       </c>
       <c r="O25" s="2" t="n">
@@ -4014,12 +4230,12 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7112920000</t>
+          <t>7112300000</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>WASTE AND SCRAP OF PRECIOUS METAL</t>
+          <t>ANODE SLIME (HASIL PEMURNIAN TEMBAGA)</t>
         </is>
       </c>
       <c r="R25" s="2" t="n">
@@ -4042,25 +4258,25 @@
         <v>15500</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>25000</v>
+        <v>310000</v>
       </c>
       <c r="X25" s="5" t="n">
-        <v>0.05</v>
+        <v>0.075</v>
       </c>
       <c r="Y25" s="5" t="n">
-        <v>19375000</v>
+        <v>0</v>
       </c>
       <c r="Z25" s="5" t="n">
-        <v>5812500</v>
+        <v>0</v>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>H</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>MERAH</t>
+          <t>HIJAU</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -4075,24 +4291,24 @@
       </c>
       <c r="AE25" s="2" t="inlineStr">
         <is>
-          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-09-11)</t>
+          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-09-01)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>07000000022220260903100025</t>
+          <t>07000000022220260906100025</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>004286</t>
+          <t>008190</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -4112,12 +4328,12 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>09.206.***.*-856.000</t>
+          <t>02.142.***.*-391.000</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>01.813.***.*-876.000</t>
+          <t>01.813.***.*-233.000</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -4132,7 +4348,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -4142,12 +4358,12 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="O26" s="2" t="n">
@@ -4155,7 +4371,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7112991000</t>
+          <t>7112920000</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -4164,7 +4380,7 @@
         </is>
       </c>
       <c r="R26" s="2" t="n">
-        <v>5200</v>
+        <v>31500</v>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
@@ -4172,7 +4388,7 @@
         </is>
       </c>
       <c r="T26" s="2" t="n">
-        <v>5200</v>
+        <v>31500</v>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
@@ -4183,25 +4399,25 @@
         <v>15500</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>75000</v>
+        <v>48000</v>
       </c>
       <c r="X26" s="5" t="n">
         <v>0.075</v>
       </c>
       <c r="Y26" s="5" t="n">
-        <v>0</v>
+        <v>55800000</v>
       </c>
       <c r="Z26" s="5" t="n">
-        <v>0</v>
+        <v>11160000</v>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>H</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>KUNING</t>
+          <t>HIJAU</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -4216,29 +4432,29 @@
       </c>
       <c r="AE26" s="2" t="inlineStr">
         <is>
-          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-09-03)</t>
+          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-09-06)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>07000000022220260804100026</t>
+          <t>07000000022220260922100026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>008200</t>
+          <t>006951</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>KPPBC TMP TANJUNG PRIOK</t>
+          <t>KPPBC TMP SOEKARNO HATTA</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -4248,17 +4464,17 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>PT AST*** AGRO LESTARI</t>
+          <t>PT MAY*** INDAH TBK</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>04.646.***.*-995.000</t>
+          <t>09.121.***.*-289.000</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>01.813.***.*-606.000</t>
+          <t>01.813.***.*-364.000</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -4273,7 +4489,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Belanda</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -4283,12 +4499,12 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>Belanda</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Belanda</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="O27" s="2" t="n">
@@ -4296,16 +4512,16 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>7112920000</t>
+          <t>7112999000</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>ELECTRONIC SCRAP CONTAINING GOLD</t>
+          <t>ANODE SLIME (HASIL PEMURNIAN TEMBAGA)</t>
         </is>
       </c>
       <c r="R27" s="2" t="n">
-        <v>15400</v>
+        <v>10650</v>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
@@ -4313,7 +4529,7 @@
         </is>
       </c>
       <c r="T27" s="2" t="n">
-        <v>15400</v>
+        <v>10650</v>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
@@ -4324,25 +4540,25 @@
         <v>15500</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>48000</v>
+        <v>310000</v>
       </c>
       <c r="X27" s="5" t="n">
         <v>0.15</v>
       </c>
       <c r="Y27" s="5" t="n">
-        <v>0</v>
+        <v>720750000</v>
       </c>
       <c r="Z27" s="5" t="n">
-        <v>0</v>
+        <v>72075000</v>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>H</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>KUNING</t>
+          <t>HIJAU</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -4357,49 +4573,49 @@
       </c>
       <c r="AE27" s="2" t="inlineStr">
         <is>
-          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-08-04)</t>
+          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-09-22)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>07000000022220260822100027</t>
+          <t>07000000022220260917100027</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>007993</t>
+          <t>001886</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>KPPBC TMP BELAWAN</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>KPPBC TMP TANJUNG PRIOK</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>KPPBC TMP TANJUNG PERAK</t>
-        </is>
-      </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>PT MAY*** INDAH TBK</t>
+          <t>PT KRA*** STEEL</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>09.601.***.*-966.000</t>
+          <t>04.102.***.*-905.000</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>01.813.***.*-887.000</t>
+          <t>01.813.***.*-149.000</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -4414,7 +4630,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapura</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -4424,12 +4640,12 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapura</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapura</t>
         </is>
       </c>
       <c r="O28" s="2" t="n">
@@ -4437,16 +4653,16 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7112991000</t>
+          <t>7112999000</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>ANODE SLIME (HASIL PEMURNIAN TEMBAGA)</t>
+          <t>WASTE AND SCRAP OF PRECIOUS METAL</t>
         </is>
       </c>
       <c r="R28" s="2" t="n">
-        <v>15400</v>
+        <v>10650</v>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
@@ -4454,7 +4670,7 @@
         </is>
       </c>
       <c r="T28" s="2" t="n">
-        <v>15400</v>
+        <v>10650</v>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
@@ -4465,25 +4681,25 @@
         <v>15500</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>48000</v>
+        <v>520000</v>
       </c>
       <c r="X28" s="5" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="Y28" s="5" t="n">
-        <v>37200000</v>
+        <v>0</v>
       </c>
       <c r="Z28" s="5" t="n">
-        <v>11160000</v>
+        <v>0</v>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>M</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>HIJAU</t>
+          <t>MERAH</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -4498,29 +4714,29 @@
       </c>
       <c r="AE28" s="2" t="inlineStr">
         <is>
-          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-08-22)</t>
+          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-09-17)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>07000000022220260713100028</t>
+          <t>07000000022220260918100028</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>008611</t>
+          <t>007773</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>KPPBC TMP BELAWAN</t>
+          <t>KPPBC TMP TANJUNG PERAK</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -4530,17 +4746,17 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>PT MAY*** INDAH TBK</t>
+          <t>PT UNI*** INDONESIA</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>08.484.***.*-399.000</t>
+          <t>01.410.***.*-522.000</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>01.813.***.*-624.000</t>
+          <t>01.813.***.*-620.000</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -4555,7 +4771,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Amerika Serikat</t>
+          <t>Tiongkok</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -4565,12 +4781,12 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>Amerika Serikat</t>
+          <t>Tiongkok</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Amerika Serikat</t>
+          <t>Tiongkok</t>
         </is>
       </c>
       <c r="O29" s="2" t="n">
@@ -4578,16 +4794,16 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7112300000</t>
+          <t>7112999000</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>SILVER CHAIN SCRAPS</t>
+          <t>ELECTRONIC SCRAP CONTAINING GOLD</t>
         </is>
       </c>
       <c r="R29" s="2" t="n">
-        <v>22000</v>
+        <v>10650</v>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
@@ -4595,7 +4811,7 @@
         </is>
       </c>
       <c r="T29" s="2" t="n">
-        <v>22000</v>
+        <v>10650</v>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
@@ -4606,25 +4822,25 @@
         <v>15500</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>75000</v>
+        <v>240000</v>
       </c>
       <c r="X29" s="5" t="n">
         <v>0.1</v>
       </c>
       <c r="Y29" s="5" t="n">
-        <v>116250000</v>
+        <v>372000000</v>
       </c>
       <c r="Z29" s="5" t="n">
-        <v>17437500</v>
+        <v>55800000</v>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>K</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>HIJAU</t>
+          <t>KUNING</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4639,24 +4855,24 @@
       </c>
       <c r="AE29" s="2" t="inlineStr">
         <is>
-          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-07-13)</t>
+          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-09-18)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>07000000022220260806100029</t>
+          <t>07000000022220260805100029</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>001821</t>
+          <t>007621</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -4671,17 +4887,17 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>PT MAY*** INDAH TBK</t>
+          <t>PT KAL*** FARMA TBK</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>01.375.***.*-516.000</t>
+          <t>08.716.***.*-231.000</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>01.813.***.*-229.000</t>
+          <t>01.813.***.*-597.000</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -4696,7 +4912,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Tiongkok</t>
+          <t>Singapura</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -4706,12 +4922,12 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>Tiongkok</t>
+          <t>Singapura</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Tiongkok</t>
+          <t>Singapura</t>
         </is>
       </c>
       <c r="O30" s="2" t="n">
@@ -4719,16 +4935,16 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7112920000</t>
+          <t>7112999000</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>SILVER CHAIN SCRAPS</t>
+          <t>WASTE AND SCRAP OF PRECIOUS METAL</t>
         </is>
       </c>
       <c r="R30" s="2" t="n">
-        <v>10650</v>
+        <v>31500</v>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
@@ -4736,7 +4952,7 @@
         </is>
       </c>
       <c r="T30" s="2" t="n">
-        <v>10650</v>
+        <v>31500</v>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
@@ -4747,10 +4963,10 @@
         <v>15500</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>25000</v>
+        <v>185000</v>
       </c>
       <c r="X30" s="5" t="n">
-        <v>0.075</v>
+        <v>0.1</v>
       </c>
       <c r="Y30" s="5" t="n">
         <v>0</v>
@@ -4760,12 +4976,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>M</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>HIJAU</t>
+          <t>MERAH</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4780,29 +4996,29 @@
       </c>
       <c r="AE30" s="2" t="inlineStr">
         <is>
-          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-08-06)</t>
+          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-08-05)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>07000000022220260730100030</t>
+          <t>07000000022220260713100030</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>002551</t>
+          <t>003562</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>KPPBC TMP BELAWAN</t>
+          <t>KPPBC TMP TANJUNG PERAK</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -4812,17 +5028,17 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>PT KAL*** FARMA TBK</t>
+          <t>PT UNI*** INDONESIA</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>03.752.***.*-488.000</t>
+          <t>07.511.***.*-519.000</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>01.813.***.*-425.000</t>
+          <t>01.813.***.*-589.000</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -4837,7 +5053,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>Jepang</t>
+          <t>Amerika Serikat</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -4847,12 +5063,12 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>Jepang</t>
+          <t>Amerika Serikat</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Jepang</t>
+          <t>Amerika Serikat</t>
         </is>
       </c>
       <c r="O31" s="2" t="n">
@@ -4860,16 +5076,16 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7112991000</t>
+          <t>7112999000</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>SILVER CHAIN SCRAPS</t>
+          <t>WASTE AND SCRAP OF PRECIOUS METAL</t>
         </is>
       </c>
       <c r="R31" s="2" t="n">
-        <v>15400</v>
+        <v>22000</v>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
@@ -4877,7 +5093,7 @@
         </is>
       </c>
       <c r="T31" s="2" t="n">
-        <v>15400</v>
+        <v>22000</v>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
@@ -4888,25 +5104,25 @@
         <v>15500</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>310000</v>
+        <v>240000</v>
       </c>
       <c r="X31" s="5" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="Y31" s="5" t="n">
-        <v>480500000</v>
+        <v>0</v>
       </c>
       <c r="Z31" s="5" t="n">
-        <v>72075000</v>
+        <v>0</v>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>M</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>HIJAU</t>
+          <t>MERAH</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4921,36 +5137,36 @@
       </c>
       <c r="AE31" s="2" t="inlineStr">
         <is>
-          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-07-30)</t>
+          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-07-13)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>07000000022220260929100031</t>
+          <t>07000000022220260806100031</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>008456</t>
+          <t>003354</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>KPPBC TMP SOEKARNO HATTA</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>KPPBC TMP TANJUNG PRIOK</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>KPPBC TMP TANJUNG PRIOK</t>
-        </is>
-      </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
           <t>PT MAY*** INDAH TBK</t>
@@ -4958,12 +5174,12 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>06.349.***.*-419.000</t>
+          <t>08.563.***.*-290.000</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>01.813.***.*-591.000</t>
+          <t>01.813.***.*-856.000</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -4978,7 +5194,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Amerika Serikat</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -4988,12 +5204,12 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>Amerika Serikat</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Amerika Serikat</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="O32" s="2" t="n">
@@ -5001,7 +5217,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7112999000</t>
+          <t>7112300000</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -5010,7 +5226,7 @@
         </is>
       </c>
       <c r="R32" s="2" t="n">
-        <v>31500</v>
+        <v>15400</v>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
@@ -5018,7 +5234,7 @@
         </is>
       </c>
       <c r="T32" s="2" t="n">
-        <v>31500</v>
+        <v>15400</v>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
@@ -5029,25 +5245,25 @@
         <v>15500</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>25000</v>
+        <v>75000</v>
       </c>
       <c r="X32" s="5" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="Y32" s="5" t="n">
-        <v>38750000</v>
+        <v>174375000</v>
       </c>
       <c r="Z32" s="5" t="n">
-        <v>5812500</v>
+        <v>17437500</v>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>M</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>KUNING</t>
+          <t>MERAH</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -5062,49 +5278,49 @@
       </c>
       <c r="AE32" s="2" t="inlineStr">
         <is>
-          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-09-29)</t>
+          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-08-06)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>07000000022220260814100032</t>
+          <t>07000000022220260901100032</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>004262</t>
+          <t>004608</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>KPPBC TMP TANJUNG PRIOK</t>
+          <t>KPPBC TMP BELAWAN</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>KPPBC TMP TANJUNG PERAK</t>
+          <t>KPPBC TMP BELAWAN</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>PT KRA*** STEEL</t>
+          <t>PT UNI*** INDONESIA</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>09.807.***.*-787.000</t>
+          <t>04.838.***.*-584.000</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>01.813.***.*-202.000</t>
+          <t>01.813.***.*-481.000</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -5119,7 +5335,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Tiongkok</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -5129,12 +5345,12 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Tiongkok</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Tiongkok</t>
         </is>
       </c>
       <c r="O33" s="2" t="n">
@@ -5142,16 +5358,16 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>7112991000</t>
+          <t>7112920000</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>SILVER CHAIN SCRAPS</t>
+          <t>ELECTRONIC SCRAP CONTAINING GOLD</t>
         </is>
       </c>
       <c r="R33" s="2" t="n">
-        <v>5200</v>
+        <v>10650</v>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
@@ -5159,7 +5375,7 @@
         </is>
       </c>
       <c r="T33" s="2" t="n">
-        <v>5200</v>
+        <v>10650</v>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
@@ -5173,22 +5389,22 @@
         <v>120000</v>
       </c>
       <c r="X33" s="5" t="n">
-        <v>0.075</v>
+        <v>0.05</v>
       </c>
       <c r="Y33" s="5" t="n">
-        <v>0</v>
+        <v>93000000</v>
       </c>
       <c r="Z33" s="5" t="n">
-        <v>0</v>
+        <v>27900000</v>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>M</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>HIJAU</t>
+          <t>MERAH</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -5203,49 +5419,49 @@
       </c>
       <c r="AE33" s="2" t="inlineStr">
         <is>
-          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-08-14)</t>
+          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-09-01)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>07000000022220260824100033</t>
+          <t>07000000022220260819100033</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>007288</t>
+          <t>006958</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>KPPBC TMP TANJUNG PRIOK</t>
+          <t>KPPBC TMP BELAWAN</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>KPPBC TMP TANJUNG PRIOK</t>
+          <t>KPPBC TMP TANJUNG PERAK</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>PT AST*** AGRO LESTARI</t>
+          <t>PT IND*** CBP MAKMUR</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>07.152.***.*-945.000</t>
+          <t>09.866.***.*-997.000</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>01.813.***.*-767.000</t>
+          <t>01.813.***.*-810.000</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -5260,7 +5476,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>Tiongkok</t>
+          <t>Jepang</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -5270,12 +5486,12 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>Tiongkok</t>
+          <t>Jepang</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Tiongkok</t>
+          <t>Jepang</t>
         </is>
       </c>
       <c r="O34" s="2" t="n">
@@ -5288,7 +5504,7 @@
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>ANODE SLIME (HASIL PEMURNIAN TEMBAGA)</t>
+          <t>SILVER CHAIN SCRAPS</t>
         </is>
       </c>
       <c r="R34" s="2" t="n">
@@ -5311,16 +5527,16 @@
         <v>15500</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>75000</v>
+        <v>310000</v>
       </c>
       <c r="X34" s="5" t="n">
         <v>0.1</v>
       </c>
       <c r="Y34" s="5" t="n">
-        <v>116250000</v>
+        <v>480500000</v>
       </c>
       <c r="Z34" s="5" t="n">
-        <v>17437500</v>
+        <v>72075000</v>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
@@ -5344,49 +5560,49 @@
       </c>
       <c r="AE34" s="2" t="inlineStr">
         <is>
-          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-08-24)</t>
+          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-08-19)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>07000000022220260829100034</t>
+          <t>07000000022220260907100034</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>001021</t>
+          <t>001495</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>KPPBC TMP SOEKARNO HATTA</t>
+          <t>KPPBC TMP BELAWAN</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>KPPBC TMP TANJUNG PERAK</t>
+          <t>KPPBC TMP BELAWAN</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>PT MAY*** INDAH TBK</t>
+          <t>PT UNI*** INDONESIA</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>04.844.***.*-362.000</t>
+          <t>07.102.***.*-271.000</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>01.813.***.*-139.000</t>
+          <t>01.813.***.*-987.000</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -5401,7 +5617,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Jepang</t>
+          <t>Amerika Serikat</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -5411,12 +5627,12 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>Jepang</t>
+          <t>Amerika Serikat</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Jepang</t>
+          <t>Amerika Serikat</t>
         </is>
       </c>
       <c r="O35" s="2" t="n">
@@ -5452,16 +5668,16 @@
         <v>15500</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>310000</v>
+        <v>48000</v>
       </c>
       <c r="X35" s="5" t="n">
-        <v>0.05</v>
+        <v>0.075</v>
       </c>
       <c r="Y35" s="5" t="n">
-        <v>240250000</v>
+        <v>0</v>
       </c>
       <c r="Z35" s="5" t="n">
-        <v>72075000</v>
+        <v>0</v>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
@@ -5485,36 +5701,36 @@
       </c>
       <c r="AE35" s="2" t="inlineStr">
         <is>
-          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-08-29)</t>
+          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-09-07)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>07000000022220260821100035</t>
+          <t>07000000022220260726100035</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>001093</t>
+          <t>008434</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>KPPBC TMP TANJUNG PRIOK</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>KPPBC TMP BELAWAN</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>KPPBC TMP TANJUNG PERAK</t>
-        </is>
-      </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
           <t>PT AST*** AGRO LESTARI</t>
@@ -5522,12 +5738,12 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>06.557.***.*-471.000</t>
+          <t>02.686.***.*-281.000</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>01.813.***.*-196.000</t>
+          <t>01.813.***.*-770.000</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -5542,7 +5758,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Amerika Serikat</t>
+          <t>India</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -5552,12 +5768,12 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>Amerika Serikat</t>
+          <t>India</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Amerika Serikat</t>
+          <t>India</t>
         </is>
       </c>
       <c r="O36" s="2" t="n">
@@ -5565,12 +5781,12 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>7112300000</t>
+          <t>7112991000</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>SILVER CHAIN SCRAPS</t>
+          <t>WASTE AND SCRAP OF PRECIOUS METAL</t>
         </is>
       </c>
       <c r="R36" s="2" t="n">
@@ -5593,25 +5809,25 @@
         <v>15500</v>
       </c>
       <c r="W36" s="4" t="n">
-        <v>25000</v>
+        <v>310000</v>
       </c>
       <c r="X36" s="5" t="n">
-        <v>0.1</v>
+        <v>0.075</v>
       </c>
       <c r="Y36" s="5" t="n">
-        <v>38750000</v>
+        <v>360375000</v>
       </c>
       <c r="Z36" s="5" t="n">
-        <v>5812500</v>
+        <v>72075000</v>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>M</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>KUNING</t>
+          <t>MERAH</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -5626,11 +5842,76 @@
       </c>
       <c r="AE36" s="2" t="inlineStr">
         <is>
-          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-08-21)</t>
-        </is>
-      </c>
+          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-07-26)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL / SUB-TOTAL</t>
+        </is>
+      </c>
+      <c r="B37" s="7">
+        <f>SUBTOTAL(103, B2:B36)</f>
+        <v/>
+      </c>
+      <c r="C37" s="8" t="n"/>
+      <c r="D37" s="8" t="n"/>
+      <c r="E37" s="8" t="n"/>
+      <c r="F37" s="8" t="n"/>
+      <c r="G37" s="8" t="n"/>
+      <c r="H37" s="8" t="n"/>
+      <c r="I37" s="8" t="n"/>
+      <c r="J37" s="8" t="n"/>
+      <c r="K37" s="8" t="n"/>
+      <c r="L37" s="8" t="n"/>
+      <c r="M37" s="8" t="n"/>
+      <c r="N37" s="8" t="n"/>
+      <c r="O37" s="9">
+        <f>SUBTOTAL(109, O2:O36)</f>
+        <v/>
+      </c>
+      <c r="P37" s="8" t="n"/>
+      <c r="Q37" s="8" t="n"/>
+      <c r="R37" s="9">
+        <f>SUBTOTAL(109, R2:R36)</f>
+        <v/>
+      </c>
+      <c r="S37" s="8" t="n"/>
+      <c r="T37" s="9">
+        <f>SUBTOTAL(109, T2:T36)</f>
+        <v/>
+      </c>
+      <c r="U37" s="8" t="n"/>
+      <c r="V37" s="9">
+        <f>SUBTOTAL(109, V2:V36)</f>
+        <v/>
+      </c>
+      <c r="W37" s="10">
+        <f>SUBTOTAL(109, W2:W36)</f>
+        <v/>
+      </c>
+      <c r="X37" s="11">
+        <f>SUBTOTAL(101, X2:X36)</f>
+        <v/>
+      </c>
+      <c r="Y37" s="12">
+        <f>SUBTOTAL(109, Y2:Y36)</f>
+        <v/>
+      </c>
+      <c r="Z37" s="12">
+        <f>SUBTOTAL(109, Z2:Z36)</f>
+        <v/>
+      </c>
+      <c r="AA37" s="8" t="n"/>
+      <c r="AB37" s="8" t="n"/>
+      <c r="AC37" s="8" t="n"/>
+      <c r="AD37" s="8" t="n"/>
+      <c r="AE37" s="8" t="n"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AE36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5641,7 +5922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -5649,180 +5930,204 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>LOG AUDIT &amp; PROVENANCE DATA PERMOHONAN</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>ID Dokumen Permohonan</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>REQ-2026-BC-089</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Judul Permohonan</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>FORMULIR RESMI PERMOHONAN AKSES &amp; EKSTRAKSI DATA KEPABEANAN</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Nama Pemohon</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>Ahmad Fauzi, S.Kom</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Unit Kerja / Divisi</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>Internal Bea dan Cukai</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Tipe Proses Bisnis</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>Ekspor</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Tujuan Penggunaan Data</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Periode Data</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>01 Juli 2026 s/d 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Katalog Sumber</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>OpenMetadata Enterprise Catalog (Verified)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Status Verifikasi</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>APPROVED (Agent-Independent-Auditor-v2)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>Waktu Verifikasi</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-11T15:11:06.341382+00:00</t>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-13T04:50:30.460650+00:00</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Jumlah Baris Diekstrak</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>35</t>
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>Dasar Regulasi PDP</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>UU No. 27/2022 jo. PP No. 33/2026 (LNRI 2026 No. 88)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>Proteksi PII / PDP</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Aktif (Masking Dinamis NPWP, NIK, Nama, dan No HP sesuai UU PDP No. 27/2022)</t>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>Aktif (Masking Dinamis NPWP, NIK, Nama, dan No HP - Ps. 123 PP 33/2026)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>Masa Retensi Wajib</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>Maksimal 30 hari kalender sejak penyerahan (Ps. 75 PP 33/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>Kewajiban Sanitasi / CoD</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>Wajib cryptographic wipe &amp; menerbitkan Certificate of Destruction ke DIKC DJBC</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>Cryptographic Digital Fingerprint</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>SHA256:a055d33cceb447143bec638e6c12f91713aed0dbfd2bc0e41ace9a03bb213cab</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>SHA256:b3fe4e4b138a369c7016421fcf6cfe171025504458ecc16300cd48b854cef48d</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>QUERY SQL YANG DIJALANKAN:</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>-- ====================================================================
--- Query Otomatis Dibuat oleh DataRequest2Agent
+-- Query Otomatis Dibuat oleh DataRequestStudio
 -- Berdasarkan Dokumen: FORMULIR RESMI PERMOHONAN AKSES &amp; EKSTRAKSI DATA KEPABEANAN (ID: REQ-2026-BC-089)
 -- Pemohon: Ahmad Fauzi, S.Kom (Internal Bea dan Cukai)
 -- Metadata Divalidasi via: OpenMetadata Service CEISA40-PostgreSQL-DWH
@@ -5869,34 +6174,34 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>Nama Kolom</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="18" t="inlineStr">
         <is>
           <t>Tipe Data</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="18" t="inlineStr">
         <is>
           <t>Deskripsi Resmi OpenMetadata</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="18" t="inlineStr">
         <is>
           <t>Klasifikasi PII</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="18" t="inlineStr">
         <is>
           <t>Tabel Sumber</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>nomor_aju</t>
         </is>
@@ -5923,7 +6228,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>nomor_daftar</t>
         </is>
@@ -5950,7 +6255,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>nomor_peb</t>
         </is>
@@ -5977,7 +6282,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>tanggal_daftar</t>
         </is>
@@ -6004,7 +6309,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>tanggal_peb</t>
         </is>
@@ -6031,7 +6336,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>kantor_ekspor</t>
         </is>
@@ -6058,7 +6363,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>kantor_muat</t>
         </is>
@@ -6085,7 +6390,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>kode_kantor</t>
         </is>
@@ -6112,7 +6417,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>npwp_eksportir</t>
         </is>
@@ -6139,7 +6444,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>nama_eksportir</t>
         </is>
@@ -6166,7 +6471,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>alamat_eksportir</t>
         </is>
@@ -6193,7 +6498,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>npwp_ppjk</t>
         </is>
@@ -6220,7 +6525,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>nama_ppjk</t>
         </is>
@@ -6247,7 +6552,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>nama_penerima</t>
         </is>
@@ -6274,7 +6579,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>negara_penerima</t>
         </is>
@@ -6301,7 +6606,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>nama_pembeli</t>
         </is>
@@ -6328,7 +6633,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>negara_pembeli</t>
         </is>
@@ -6355,7 +6660,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>negara_tujuan</t>
         </is>
@@ -6382,7 +6687,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>seri_barang</t>
         </is>
@@ -6409,7 +6714,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>kode_hs</t>
         </is>
@@ -6436,7 +6741,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>uraian_barang</t>
         </is>
@@ -6463,7 +6768,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>jumlah_satuan</t>
         </is>
@@ -6490,7 +6795,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>jenis_satuan</t>
         </is>
@@ -6517,7 +6822,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>netto_barang</t>
         </is>
@@ -6544,7 +6849,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>valuta</t>
         </is>
@@ -6571,7 +6876,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>kurs</t>
         </is>
@@ -6598,7 +6903,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>fob_barang</t>
         </is>
@@ -6625,7 +6930,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>nilai_fob_usd</t>
         </is>
@@ -6652,7 +6957,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="inlineStr">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>nilai_devisa_idr</t>
         </is>
@@ -6679,7 +6984,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="inlineStr">
+      <c r="A31" s="19" t="inlineStr">
         <is>
           <t>tarif_bea_keluar</t>
         </is>
@@ -6706,7 +7011,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="inlineStr">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>bea_keluar_barang</t>
         </is>
@@ -6733,7 +7038,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="inlineStr">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>pph_ekspor_peb</t>
         </is>
@@ -6760,7 +7065,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="inlineStr">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>jalur</t>
         </is>
@@ -6787,7 +7092,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="12" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>status_pabean</t>
         </is>
@@ -6814,7 +7119,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="12" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
@@ -6841,7 +7146,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="12" t="inlineStr">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>nomor_aju</t>
         </is>
@@ -6868,7 +7173,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="12" t="inlineStr">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>nomor_daftar</t>
         </is>
@@ -6895,7 +7200,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="12" t="inlineStr">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>tanggal_daftar</t>
         </is>
@@ -6922,7 +7227,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="12" t="inlineStr">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>kantor_ekspor</t>
         </is>
@@ -6949,7 +7254,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="12" t="inlineStr">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t>kantor_muat</t>
         </is>
@@ -6976,7 +7281,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="12" t="inlineStr">
+      <c r="A42" s="19" t="inlineStr">
         <is>
           <t>npwp_eksportir</t>
         </is>
@@ -7003,7 +7308,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="12" t="inlineStr">
+      <c r="A43" s="19" t="inlineStr">
         <is>
           <t>nama_eksportir</t>
         </is>
@@ -7030,7 +7335,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="12" t="inlineStr">
+      <c r="A44" s="19" t="inlineStr">
         <is>
           <t>alamat_eksportir</t>
         </is>
@@ -7057,7 +7362,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="12" t="inlineStr">
+      <c r="A45" s="19" t="inlineStr">
         <is>
           <t>npwp_ppjk</t>
         </is>
@@ -7084,7 +7389,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="12" t="inlineStr">
+      <c r="A46" s="19" t="inlineStr">
         <is>
           <t>nama_ppjk</t>
         </is>
@@ -7111,7 +7416,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="12" t="inlineStr">
+      <c r="A47" s="19" t="inlineStr">
         <is>
           <t>nama_penerima</t>
         </is>
@@ -7138,7 +7443,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="12" t="inlineStr">
+      <c r="A48" s="19" t="inlineStr">
         <is>
           <t>negara_penerima</t>
         </is>
@@ -7165,7 +7470,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="12" t="inlineStr">
+      <c r="A49" s="19" t="inlineStr">
         <is>
           <t>nama_pembeli</t>
         </is>
@@ -7192,7 +7497,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="12" t="inlineStr">
+      <c r="A50" s="19" t="inlineStr">
         <is>
           <t>negara_pembeli</t>
         </is>
@@ -7219,7 +7524,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="12" t="inlineStr">
+      <c r="A51" s="19" t="inlineStr">
         <is>
           <t>negara_tujuan</t>
         </is>
@@ -7246,7 +7551,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="12" t="inlineStr">
+      <c r="A52" s="19" t="inlineStr">
         <is>
           <t>seri_barang</t>
         </is>
@@ -7273,7 +7578,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="12" t="inlineStr">
+      <c r="A53" s="19" t="inlineStr">
         <is>
           <t>kode_hs</t>
         </is>
@@ -7300,7 +7605,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="12" t="inlineStr">
+      <c r="A54" s="19" t="inlineStr">
         <is>
           <t>uraian_barang</t>
         </is>
@@ -7327,7 +7632,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="12" t="inlineStr">
+      <c r="A55" s="19" t="inlineStr">
         <is>
           <t>jumlah_satuan</t>
         </is>
@@ -7354,7 +7659,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="12" t="inlineStr">
+      <c r="A56" s="19" t="inlineStr">
         <is>
           <t>jenis_satuan</t>
         </is>
@@ -7381,7 +7686,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="12" t="inlineStr">
+      <c r="A57" s="19" t="inlineStr">
         <is>
           <t>netto_barang</t>
         </is>
@@ -7408,7 +7713,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="12" t="inlineStr">
+      <c r="A58" s="19" t="inlineStr">
         <is>
           <t>valuta</t>
         </is>
@@ -7435,7 +7740,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="12" t="inlineStr">
+      <c r="A59" s="19" t="inlineStr">
         <is>
           <t>kurs</t>
         </is>
@@ -7462,7 +7767,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="12" t="inlineStr">
+      <c r="A60" s="19" t="inlineStr">
         <is>
           <t>fob_barang</t>
         </is>
@@ -7489,7 +7794,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="12" t="inlineStr">
+      <c r="A61" s="19" t="inlineStr">
         <is>
           <t>tarif_bea_keluar</t>
         </is>
@@ -7516,7 +7821,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="12" t="inlineStr">
+      <c r="A62" s="19" t="inlineStr">
         <is>
           <t>bea_keluar_barang</t>
         </is>
@@ -7543,7 +7848,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="12" t="inlineStr">
+      <c r="A63" s="19" t="inlineStr">
         <is>
           <t>pph_ekspor_peb</t>
         </is>
@@ -7570,7 +7875,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="12" t="inlineStr">
+      <c r="A64" s="19" t="inlineStr">
         <is>
           <t>jalur</t>
         </is>
@@ -7597,7 +7902,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="12" t="inlineStr">
+      <c r="A65" s="19" t="inlineStr">
         <is>
           <t>status_pabean</t>
         </is>
@@ -7624,7 +7929,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="12" t="inlineStr">
+      <c r="A66" s="19" t="inlineStr">
         <is>
           <t>transaction_id</t>
         </is>
@@ -7651,7 +7956,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="12" t="inlineStr">
+      <c r="A67" s="19" t="inlineStr">
         <is>
           <t>customer_id</t>
         </is>
@@ -7678,7 +7983,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="12" t="inlineStr">
+      <c r="A68" s="19" t="inlineStr">
         <is>
           <t>transaction_date</t>
         </is>
@@ -7705,7 +8010,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="12" t="inlineStr">
+      <c r="A69" s="19" t="inlineStr">
         <is>
           <t>total_amount</t>
         </is>
@@ -7732,7 +8037,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="12" t="inlineStr">
+      <c r="A70" s="19" t="inlineStr">
         <is>
           <t>status</t>
         </is>
@@ -7759,7 +8064,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="12" t="inlineStr">
+      <c r="A71" s="19" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
@@ -7786,7 +8091,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="12" t="inlineStr">
+      <c r="A72" s="19" t="inlineStr">
         <is>
           <t>customer_id</t>
         </is>
@@ -7813,7 +8118,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="12" t="inlineStr">
+      <c r="A73" s="19" t="inlineStr">
         <is>
           <t>customer_name</t>
         </is>
@@ -7840,7 +8145,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="12" t="inlineStr">
+      <c r="A74" s="19" t="inlineStr">
         <is>
           <t>email</t>
         </is>
@@ -7867,7 +8172,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="12" t="inlineStr">
+      <c r="A75" s="19" t="inlineStr">
         <is>
           <t>phone_number</t>
         </is>
@@ -7894,7 +8199,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="12" t="inlineStr">
+      <c r="A76" s="19" t="inlineStr">
         <is>
           <t>nik</t>
         </is>
@@ -7921,7 +8226,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="12" t="inlineStr">
+      <c r="A77" s="19" t="inlineStr">
         <is>
           <t>customer_segment</t>
         </is>
@@ -7948,7 +8253,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="12" t="inlineStr">
+      <c r="A78" s="19" t="inlineStr">
         <is>
           <t>city</t>
         </is>
@@ -7975,7 +8280,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="12" t="inlineStr">
+      <c r="A79" s="19" t="inlineStr">
         <is>
           <t>province</t>
         </is>
@@ -8002,7 +8307,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="12" t="inlineStr">
+      <c r="A80" s="19" t="inlineStr">
         <is>
           <t>registration_date</t>
         </is>
@@ -8029,7 +8334,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="12" t="inlineStr">
+      <c r="A81" s="19" t="inlineStr">
         <is>
           <t>is_active</t>
         </is>
@@ -8058,4 +8363,1646 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="32" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>PROFILING &amp; METRIK KUALITAS DATA KEPABEANAN (DATA QUALITY SCORECARD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>Permohonan: REQ-2026-BC-089 | Tanggal Analisis: 13 October 2026 | Total Baris: 35 baris</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t>SKOR KELENGKAPAN</t>
+        </is>
+      </c>
+      <c r="E4" s="23" t="inlineStr">
+        <is>
+          <t>TOTAL ATRIBUT</t>
+        </is>
+      </c>
+      <c r="H4" s="24" t="inlineStr">
+        <is>
+          <t>KOLOM PROTEKSI PDP</t>
+        </is>
+      </c>
+      <c r="K4" s="25" t="inlineStr">
+        <is>
+          <t>STATUS INTEGRITAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="26">
+        <f>AVERAGE(G9:G39)</f>
+        <v/>
+      </c>
+      <c r="E5" s="27">
+        <f>COUNTA(B9:B39)</f>
+        <v/>
+      </c>
+      <c r="H5" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="K5" s="29" t="inlineStr">
+        <is>
+          <t>100% VALID &amp; VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>Nama Atribut / Kolom</t>
+        </is>
+      </c>
+      <c r="C8" s="30" t="inlineStr">
+        <is>
+          <t>Tipe Data Terdeteksi</t>
+        </is>
+      </c>
+      <c r="D8" s="30" t="inlineStr">
+        <is>
+          <t>Total Baris</t>
+        </is>
+      </c>
+      <c r="E8" s="30" t="inlineStr">
+        <is>
+          <t>Terisi (Non-Null)</t>
+        </is>
+      </c>
+      <c r="F8" s="30" t="inlineStr">
+        <is>
+          <t>Kosong (Null)</t>
+        </is>
+      </c>
+      <c r="G8" s="30" t="inlineStr">
+        <is>
+          <t>Rasio Kelengkapan</t>
+        </is>
+      </c>
+      <c r="H8" s="30" t="inlineStr">
+        <is>
+          <t>Nilai Unik (Kardinalitas)</t>
+        </is>
+      </c>
+      <c r="I8" s="30" t="inlineStr">
+        <is>
+          <t>Nilai Modus / Terbanyak</t>
+        </is>
+      </c>
+      <c r="J8" s="30" t="inlineStr">
+        <is>
+          <t>Frekuensi</t>
+        </is>
+      </c>
+      <c r="K8" s="30" t="inlineStr">
+        <is>
+          <t>Rentang / Statistik Sebaran</t>
+        </is>
+      </c>
+      <c r="L8" s="30" t="inlineStr">
+        <is>
+          <t>Status Kepatuhan PDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="32" t="inlineStr">
+        <is>
+          <t>nomor_aju</t>
+        </is>
+      </c>
+      <c r="C9" s="32" t="inlineStr">
+        <is>
+          <t>String / Teks Kategoris</t>
+        </is>
+      </c>
+      <c r="D9" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="E9" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="F9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="I9" s="32" t="inlineStr">
+        <is>
+          <t>07000000022220260704100001</t>
+        </is>
+      </c>
+      <c r="J9" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="35" t="inlineStr">
+        <is>
+          <t>Kardinalitas: 35 ragam nilai</t>
+        </is>
+      </c>
+      <c r="L9" s="31" t="inlineStr">
+        <is>
+          <t>Data Transaksional Standar</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="37" t="inlineStr">
+        <is>
+          <t>nomor_daftar</t>
+        </is>
+      </c>
+      <c r="C10" s="37" t="inlineStr">
+        <is>
+          <t>String / Teks Kategoris</t>
+        </is>
+      </c>
+      <c r="D10" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="E10" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="F10" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="38" t="n">
+        <v>34</v>
+      </c>
+      <c r="I10" s="37" t="inlineStr">
+        <is>
+          <t>006951</t>
+        </is>
+      </c>
+      <c r="J10" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" s="40" t="inlineStr">
+        <is>
+          <t>Kardinalitas: 34 ragam nilai</t>
+        </is>
+      </c>
+      <c r="L10" s="36" t="inlineStr">
+        <is>
+          <t>Data Transaksional Standar</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" s="32" t="inlineStr">
+        <is>
+          <t>tanggal_daftar</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="inlineStr">
+        <is>
+          <t>Tanggal / Temporal</t>
+        </is>
+      </c>
+      <c r="D11" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="E11" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="F11" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="33" t="n">
+        <v>27</v>
+      </c>
+      <c r="I11" s="32" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J11" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" s="35" t="inlineStr">
+        <is>
+          <t>Rentang: 2026-07-04 s/d 2026-09-30</t>
+        </is>
+      </c>
+      <c r="L11" s="31" t="inlineStr">
+        <is>
+          <t>Data Transaksional Standar</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="B12" s="37" t="inlineStr">
+        <is>
+          <t>kantor_ekspor</t>
+        </is>
+      </c>
+      <c r="C12" s="37" t="inlineStr">
+        <is>
+          <t>String / Teks Kategoris</t>
+        </is>
+      </c>
+      <c r="D12" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="E12" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="F12" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="38" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" s="37" t="inlineStr">
+        <is>
+          <t>KPPBC TMP BELAWAN</t>
+        </is>
+      </c>
+      <c r="J12" s="38" t="n">
+        <v>12</v>
+      </c>
+      <c r="K12" s="40" t="inlineStr">
+        <is>
+          <t>Kardinalitas: 4 ragam nilai</t>
+        </is>
+      </c>
+      <c r="L12" s="36" t="inlineStr">
+        <is>
+          <t>Data Transaksional Standar</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="B13" s="32" t="inlineStr">
+        <is>
+          <t>kantor_muat</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="inlineStr">
+        <is>
+          <t>String / Teks Kategoris</t>
+        </is>
+      </c>
+      <c r="D13" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="E13" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="F13" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" s="32" t="inlineStr">
+        <is>
+          <t>KPPBC TMP BELAWAN</t>
+        </is>
+      </c>
+      <c r="J13" s="33" t="n">
+        <v>14</v>
+      </c>
+      <c r="K13" s="35" t="inlineStr">
+        <is>
+          <t>Kardinalitas: 3 ragam nilai</t>
+        </is>
+      </c>
+      <c r="L13" s="31" t="inlineStr">
+        <is>
+          <t>Data Transaksional Standar</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="36" t="n">
+        <v>6</v>
+      </c>
+      <c r="B14" s="37" t="inlineStr">
+        <is>
+          <t>nama_eksportir_masked</t>
+        </is>
+      </c>
+      <c r="C14" s="37" t="inlineStr">
+        <is>
+          <t>String / Teks Kategoris</t>
+        </is>
+      </c>
+      <c r="D14" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="E14" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="F14" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="38" t="n">
+        <v>6</v>
+      </c>
+      <c r="I14" s="37" t="inlineStr">
+        <is>
+          <t>PT IND*** CBP MAKMUR</t>
+        </is>
+      </c>
+      <c r="J14" s="38" t="n">
+        <v>7</v>
+      </c>
+      <c r="K14" s="40" t="inlineStr">
+        <is>
+          <t>Kardinalitas: 6 ragam nilai</t>
+        </is>
+      </c>
+      <c r="L14" s="41" t="inlineStr">
+        <is>
+          <t>Dimaskir Dinamis (Aman)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="B15" s="32" t="inlineStr">
+        <is>
+          <t>npwp_eksportir_masked</t>
+        </is>
+      </c>
+      <c r="C15" s="32" t="inlineStr">
+        <is>
+          <t>String / Teks Kategoris</t>
+        </is>
+      </c>
+      <c r="D15" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="E15" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="F15" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="I15" s="32" t="inlineStr">
+        <is>
+          <t>01.264.***.*-936.000</t>
+        </is>
+      </c>
+      <c r="J15" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="35" t="inlineStr">
+        <is>
+          <t>Kardinalitas: 35 ragam nilai</t>
+        </is>
+      </c>
+      <c r="L15" s="42" t="inlineStr">
+        <is>
+          <t>Dimaskir Dinamis (Aman)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="B16" s="37" t="inlineStr">
+        <is>
+          <t>npwp_ppjk_masked</t>
+        </is>
+      </c>
+      <c r="C16" s="37" t="inlineStr">
+        <is>
+          <t>String / Teks Kategoris</t>
+        </is>
+      </c>
+      <c r="D16" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="E16" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="F16" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="I16" s="37" t="inlineStr">
+        <is>
+          <t>01.813.***.*-125.000</t>
+        </is>
+      </c>
+      <c r="J16" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" s="40" t="inlineStr">
+        <is>
+          <t>Kardinalitas: 35 ragam nilai</t>
+        </is>
+      </c>
+      <c r="L16" s="41" t="inlineStr">
+        <is>
+          <t>Dimaskir Dinamis (Aman)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" s="32" t="inlineStr">
+        <is>
+          <t>nama_ppjk_masked</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="inlineStr">
+        <is>
+          <t>String / Teks Kategoris</t>
+        </is>
+      </c>
+      <c r="D17" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="E17" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="F17" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="32" t="inlineStr">
+        <is>
+          <t>PT CIP*** SEGARA INTERNASIONAL</t>
+        </is>
+      </c>
+      <c r="J17" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="K17" s="35" t="inlineStr">
+        <is>
+          <t>Kardinalitas: 1 ragam nilai</t>
+        </is>
+      </c>
+      <c r="L17" s="42" t="inlineStr">
+        <is>
+          <t>Dimaskir Dinamis (Aman)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="B18" s="37" t="inlineStr">
+        <is>
+          <t>nama_penerima</t>
+        </is>
+      </c>
+      <c r="C18" s="37" t="inlineStr">
+        <is>
+          <t>String / Teks Kategoris</t>
+        </is>
+      </c>
+      <c r="D18" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="E18" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="F18" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="37" t="inlineStr">
+        <is>
+          <t>MITSUBISHI CORPORATION RTM JAPAN LTD.</t>
+        </is>
+      </c>
+      <c r="J18" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="K18" s="40" t="inlineStr">
+        <is>
+          <t>Kardinalitas: 1 ragam nilai</t>
+        </is>
+      </c>
+      <c r="L18" s="36" t="inlineStr">
+        <is>
+          <t>Data Transaksional Standar</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="n">
+        <v>11</v>
+      </c>
+      <c r="B19" s="32" t="inlineStr">
+        <is>
+          <t>negara_penerima</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="inlineStr">
+        <is>
+          <t>String / Teks Kategoris</t>
+        </is>
+      </c>
+      <c r="D19" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="E19" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="F19" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="33" t="n">
+        <v>7</v>
+      </c>
+      <c r="I19" s="32" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="J19" s="33" t="n">
+        <v>8</v>
+      </c>
+      <c r="K19" s="35" t="inlineStr">
+        <is>
+          <t>Kardinalitas: 7 ragam nilai</t>
+        </is>
+      </c>
+      <c r="L19" s="31" t="inlineStr">
+        <is>
+          <t>Data Transaksional Standar</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="36" t="n">
+        <v>12</v>
+      </c>
+      <c r="B20" s="37" t="inlineStr">
+        <is>
+          <t>nama_pembeli</t>
+        </is>
+      </c>
+      <c r="C20" s="37" t="inlineStr">
+        <is>
+          <t>String / Teks Kategoris</t>
+        </is>
+      </c>
+      <c r="D20" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="E20" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="F20" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="37" t="inlineStr">
+        <is>
+          <t>MITSUBISHI CORP BUYER INC.</t>
+        </is>
+      </c>
+      <c r="J20" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="K20" s="40" t="inlineStr">
+        <is>
+          <t>Kardinalitas: 1 ragam nilai</t>
+        </is>
+      </c>
+      <c r="L20" s="36" t="inlineStr">
+        <is>
+          <t>Data Transaksional Standar</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="n">
+        <v>13</v>
+      </c>
+      <c r="B21" s="32" t="inlineStr">
+        <is>
+          <t>negara_pembeli</t>
+        </is>
+      </c>
+      <c r="C21" s="32" t="inlineStr">
+        <is>
+          <t>String / Teks Kategoris</t>
+        </is>
+      </c>
+      <c r="D21" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="E21" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="F21" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="33" t="n">
+        <v>7</v>
+      </c>
+      <c r="I21" s="32" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="J21" s="33" t="n">
+        <v>8</v>
+      </c>
+      <c r="K21" s="35" t="inlineStr">
+        <is>
+          <t>Kardinalitas: 7 ragam nilai</t>
+        </is>
+      </c>
+      <c r="L21" s="31" t="inlineStr">
+        <is>
+          <t>Data Transaksional Standar</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="36" t="n">
+        <v>14</v>
+      </c>
+      <c r="B22" s="37" t="inlineStr">
+        <is>
+          <t>negara_tujuan</t>
+        </is>
+      </c>
+      <c r="C22" s="37" t="inlineStr">
+        <is>
+          <t>String / Teks Kategoris</t>
+        </is>
+      </c>
+      <c r="D22" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="E22" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="F22" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="38" t="n">
+        <v>7</v>
+      </c>
+      <c r="I22" s="37" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="J22" s="38" t="n">
+        <v>8</v>
+      </c>
+      <c r="K22" s="40" t="inlineStr">
+        <is>
+          <t>Kardinalitas: 7 ragam nilai</t>
+        </is>
+      </c>
+      <c r="L22" s="36" t="inlineStr">
+        <is>
+          <t>Data Transaksional Standar</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="n">
+        <v>15</v>
+      </c>
+      <c r="B23" s="32" t="inlineStr">
+        <is>
+          <t>seri_barang</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="inlineStr">
+        <is>
+          <t>Numerik (Integer/Float)</t>
+        </is>
+      </c>
+      <c r="D23" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="E23" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="F23" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="K23" s="35" t="inlineStr">
+        <is>
+          <t>Min: 1, Max: 1, Avg: 1</t>
+        </is>
+      </c>
+      <c r="L23" s="31" t="inlineStr">
+        <is>
+          <t>Data Transaksional Standar</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="36" t="n">
+        <v>16</v>
+      </c>
+      <c r="B24" s="37" t="inlineStr">
+        <is>
+          <t>kode_hs</t>
+        </is>
+      </c>
+      <c r="C24" s="37" t="inlineStr">
+        <is>
+          <t>String / Teks Kategoris</t>
+        </is>
+      </c>
+      <c r="D24" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="E24" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="F24" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="38" t="n">
+        <v>4</v>
+      </c>
+      <c r="I24" s="37" t="inlineStr">
+        <is>
+          <t>7112999000</t>
+        </is>
+      </c>
+      <c r="J24" s="38" t="n">
+        <v>12</v>
+      </c>
+      <c r="K24" s="40" t="inlineStr">
+        <is>
+          <t>Kardinalitas: 4 ragam nilai</t>
+        </is>
+      </c>
+      <c r="L24" s="36" t="inlineStr">
+        <is>
+          <t>Data Transaksional Standar</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="n">
+        <v>17</v>
+      </c>
+      <c r="B25" s="32" t="inlineStr">
+        <is>
+          <t>uraian_barang</t>
+        </is>
+      </c>
+      <c r="C25" s="32" t="inlineStr">
+        <is>
+          <t>String / Teks Kategoris</t>
+        </is>
+      </c>
+      <c r="D25" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="E25" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="F25" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="I25" s="32" t="inlineStr">
+        <is>
+          <t>ANODE SLIME (HASIL PEMURNIAN TEMBAGA)</t>
+        </is>
+      </c>
+      <c r="J25" s="33" t="n">
+        <v>9</v>
+      </c>
+      <c r="K25" s="35" t="inlineStr">
+        <is>
+          <t>Kardinalitas: 4 ragam nilai</t>
+        </is>
+      </c>
+      <c r="L25" s="31" t="inlineStr">
+        <is>
+          <t>Data Transaksional Standar</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="36" t="n">
+        <v>18</v>
+      </c>
+      <c r="B26" s="37" t="inlineStr">
+        <is>
+          <t>jumlah_satuan</t>
+        </is>
+      </c>
+      <c r="C26" s="37" t="inlineStr">
+        <is>
+          <t>Numerik (Integer/Float)</t>
+        </is>
+      </c>
+      <c r="D26" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="E26" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="F26" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="38" t="n">
+        <v>5</v>
+      </c>
+      <c r="I26" s="37" t="inlineStr">
+        <is>
+          <t>10650</t>
+        </is>
+      </c>
+      <c r="J26" s="38" t="n">
+        <v>12</v>
+      </c>
+      <c r="K26" s="40" t="inlineStr">
+        <is>
+          <t>Min: 5,200, Max: 31,500, Avg: 15,434</t>
+        </is>
+      </c>
+      <c r="L26" s="36" t="inlineStr">
+        <is>
+          <t>Data Transaksional Standar</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="31" t="n">
+        <v>19</v>
+      </c>
+      <c r="B27" s="32" t="inlineStr">
+        <is>
+          <t>jenis_satuan</t>
+        </is>
+      </c>
+      <c r="C27" s="32" t="inlineStr">
+        <is>
+          <t>String / Teks Kategoris</t>
+        </is>
+      </c>
+      <c r="D27" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="E27" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="F27" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="32" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="J27" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="K27" s="35" t="inlineStr">
+        <is>
+          <t>Kardinalitas: 1 ragam nilai</t>
+        </is>
+      </c>
+      <c r="L27" s="31" t="inlineStr">
+        <is>
+          <t>Data Transaksional Standar</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B28" s="37" t="inlineStr">
+        <is>
+          <t>netto_barang</t>
+        </is>
+      </c>
+      <c r="C28" s="37" t="inlineStr">
+        <is>
+          <t>Numerik (Integer/Float)</t>
+        </is>
+      </c>
+      <c r="D28" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="E28" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="F28" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="38" t="n">
+        <v>5</v>
+      </c>
+      <c r="I28" s="37" t="inlineStr">
+        <is>
+          <t>10650</t>
+        </is>
+      </c>
+      <c r="J28" s="38" t="n">
+        <v>12</v>
+      </c>
+      <c r="K28" s="40" t="inlineStr">
+        <is>
+          <t>Min: 5,200, Max: 31,500, Avg: 15,434</t>
+        </is>
+      </c>
+      <c r="L28" s="36" t="inlineStr">
+        <is>
+          <t>Data Transaksional Standar</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="31" t="n">
+        <v>21</v>
+      </c>
+      <c r="B29" s="32" t="inlineStr">
+        <is>
+          <t>valuta</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="inlineStr">
+        <is>
+          <t>String / Teks Kategoris</t>
+        </is>
+      </c>
+      <c r="D29" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="E29" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="F29" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J29" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="K29" s="35" t="inlineStr">
+        <is>
+          <t>Kardinalitas: 1 ragam nilai</t>
+        </is>
+      </c>
+      <c r="L29" s="31" t="inlineStr">
+        <is>
+          <t>Data Transaksional Standar</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="36" t="n">
+        <v>22</v>
+      </c>
+      <c r="B30" s="37" t="inlineStr">
+        <is>
+          <t>kurs</t>
+        </is>
+      </c>
+      <c r="C30" s="37" t="inlineStr">
+        <is>
+          <t>Numerik (Integer/Float)</t>
+        </is>
+      </c>
+      <c r="D30" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="E30" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="F30" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="37" t="inlineStr">
+        <is>
+          <t>15500</t>
+        </is>
+      </c>
+      <c r="J30" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="K30" s="40" t="inlineStr">
+        <is>
+          <t>Min: 15,500, Max: 15,500, Avg: 15,500</t>
+        </is>
+      </c>
+      <c r="L30" s="36" t="inlineStr">
+        <is>
+          <t>Data Transaksional Standar</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="31" t="n">
+        <v>23</v>
+      </c>
+      <c r="B31" s="32" t="inlineStr">
+        <is>
+          <t>fob_barang</t>
+        </is>
+      </c>
+      <c r="C31" s="32" t="inlineStr">
+        <is>
+          <t>Numerik (Integer/Float)</t>
+        </is>
+      </c>
+      <c r="D31" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="E31" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="F31" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="33" t="n">
+        <v>8</v>
+      </c>
+      <c r="I31" s="32" t="inlineStr">
+        <is>
+          <t>120000</t>
+        </is>
+      </c>
+      <c r="J31" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="K31" s="35" t="inlineStr">
+        <is>
+          <t>Min: $25,000, Max: $520,000, Avg: $207,057</t>
+        </is>
+      </c>
+      <c r="L31" s="31" t="inlineStr">
+        <is>
+          <t>Data Transaksional Standar</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="36" t="n">
+        <v>24</v>
+      </c>
+      <c r="B32" s="37" t="inlineStr">
+        <is>
+          <t>tarif_bea_keluar</t>
+        </is>
+      </c>
+      <c r="C32" s="37" t="inlineStr">
+        <is>
+          <t>Numerik (Integer/Float)</t>
+        </is>
+      </c>
+      <c r="D32" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="E32" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="F32" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="38" t="n">
+        <v>4</v>
+      </c>
+      <c r="I32" s="37" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="J32" s="38" t="n">
+        <v>11</v>
+      </c>
+      <c r="K32" s="40" t="inlineStr">
+        <is>
+          <t>Min: 5.0%, Max: 15.0%, Avg: 9.0%</t>
+        </is>
+      </c>
+      <c r="L32" s="36" t="inlineStr">
+        <is>
+          <t>Data Transaksional Standar</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="31" t="n">
+        <v>25</v>
+      </c>
+      <c r="B33" s="32" t="inlineStr">
+        <is>
+          <t>bea_keluar_barang</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="inlineStr">
+        <is>
+          <t>Numerik (Integer/Float)</t>
+        </is>
+      </c>
+      <c r="D33" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="E33" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="F33" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="33" t="n">
+        <v>18</v>
+      </c>
+      <c r="I33" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J33" s="33" t="n">
+        <v>15</v>
+      </c>
+      <c r="K33" s="35" t="inlineStr">
+        <is>
+          <t>Min: 0, Max: 806,000,000, Avg: 169,503,571</t>
+        </is>
+      </c>
+      <c r="L33" s="31" t="inlineStr">
+        <is>
+          <t>Data Transaksional Standar</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="36" t="n">
+        <v>26</v>
+      </c>
+      <c r="B34" s="37" t="inlineStr">
+        <is>
+          <t>pph_ekspor_peb</t>
+        </is>
+      </c>
+      <c r="C34" s="37" t="inlineStr">
+        <is>
+          <t>Numerik (Integer/Float)</t>
+        </is>
+      </c>
+      <c r="D34" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="E34" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="F34" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="38" t="n">
+        <v>9</v>
+      </c>
+      <c r="I34" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J34" s="38" t="n">
+        <v>15</v>
+      </c>
+      <c r="K34" s="40" t="inlineStr">
+        <is>
+          <t>Min: 0, Max: 120,900,000, Avg: 28,105,929</t>
+        </is>
+      </c>
+      <c r="L34" s="36" t="inlineStr">
+        <is>
+          <t>Data Transaksional Standar</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="31" t="n">
+        <v>27</v>
+      </c>
+      <c r="B35" s="32" t="inlineStr">
+        <is>
+          <t>jalur</t>
+        </is>
+      </c>
+      <c r="C35" s="32" t="inlineStr">
+        <is>
+          <t>String / Teks Kategoris</t>
+        </is>
+      </c>
+      <c r="D35" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="E35" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="F35" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="I35" s="32" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J35" s="33" t="n">
+        <v>20</v>
+      </c>
+      <c r="K35" s="35" t="inlineStr">
+        <is>
+          <t>Kardinalitas: 3 ragam nilai</t>
+        </is>
+      </c>
+      <c r="L35" s="31" t="inlineStr">
+        <is>
+          <t>Data Transaksional Standar</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="36" t="n">
+        <v>28</v>
+      </c>
+      <c r="B36" s="37" t="inlineStr">
+        <is>
+          <t>status_jalur</t>
+        </is>
+      </c>
+      <c r="C36" s="37" t="inlineStr">
+        <is>
+          <t>String / Teks Kategoris</t>
+        </is>
+      </c>
+      <c r="D36" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="E36" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="F36" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="38" t="n">
+        <v>3</v>
+      </c>
+      <c r="I36" s="37" t="inlineStr">
+        <is>
+          <t>HIJAU</t>
+        </is>
+      </c>
+      <c r="J36" s="38" t="n">
+        <v>20</v>
+      </c>
+      <c r="K36" s="40" t="inlineStr">
+        <is>
+          <t>Kardinalitas: 3 ragam nilai</t>
+        </is>
+      </c>
+      <c r="L36" s="36" t="inlineStr">
+        <is>
+          <t>Data Transaksional Standar</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B37" s="32" t="inlineStr">
+        <is>
+          <t>status_pabean</t>
+        </is>
+      </c>
+      <c r="C37" s="32" t="inlineStr">
+        <is>
+          <t>String / Teks Kategoris</t>
+        </is>
+      </c>
+      <c r="D37" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="E37" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="F37" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="32" t="inlineStr">
+        <is>
+          <t>NPE</t>
+        </is>
+      </c>
+      <c r="J37" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="K37" s="35" t="inlineStr">
+        <is>
+          <t>Kardinalitas: 1 ragam nilai</t>
+        </is>
+      </c>
+      <c r="L37" s="31" t="inlineStr">
+        <is>
+          <t>Data Transaksional Standar</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="36" t="n">
+        <v>30</v>
+      </c>
+      <c r="B38" s="37" t="inlineStr">
+        <is>
+          <t>status_dokumen</t>
+        </is>
+      </c>
+      <c r="C38" s="37" t="inlineStr">
+        <is>
+          <t>String / Teks Kategoris</t>
+        </is>
+      </c>
+      <c r="D38" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="E38" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="F38" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="37" t="inlineStr">
+        <is>
+          <t>SELESAI (NPE)</t>
+        </is>
+      </c>
+      <c r="J38" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="K38" s="40" t="inlineStr">
+        <is>
+          <t>Kardinalitas: 1 ragam nilai</t>
+        </is>
+      </c>
+      <c r="L38" s="36" t="inlineStr">
+        <is>
+          <t>Data Transaksional Standar</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="31" t="n">
+        <v>31</v>
+      </c>
+      <c r="B39" s="32" t="inlineStr">
+        <is>
+          <t>dokumen_pelengkap</t>
+        </is>
+      </c>
+      <c r="C39" s="32" t="inlineStr">
+        <is>
+          <t>String / Teks Kategoris</t>
+        </is>
+      </c>
+      <c r="D39" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="E39" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="F39" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="33" t="n">
+        <v>27</v>
+      </c>
+      <c r="I39" s="32" t="inlineStr">
+        <is>
+          <t>INVOICE: SLMMMC2026-01 (Tgl: 2026-09-18)</t>
+        </is>
+      </c>
+      <c r="J39" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="K39" s="35" t="inlineStr">
+        <is>
+          <t>Kardinalitas: 27 ragam nilai</t>
+        </is>
+      </c>
+      <c r="L39" s="31" t="inlineStr">
+        <is>
+          <t>Data Transaksional Standar</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="B4:C4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>